--- a/input/ES/reg_leave_parental_home.xlsx
+++ b/input/ES/reg_leave_parental_home.xlsx
@@ -305,7 +305,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>0.099704479299801196</v>
+        <v>0.099704223872782327</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
@@ -313,7 +313,7 @@
         <v>20</v>
       </c>
       <c r="F5">
-        <v>749.98887612451267</v>
+        <v>749.98690927615462</v>
       </c>
     </row>
     <row r="6">
@@ -329,7 +329,7 @@
         <v>21</v>
       </c>
       <c r="F6">
-        <v>-7951365.8808215335</v>
+        <v>-7951357.9052014332</v>
       </c>
     </row>
   </sheetData>
@@ -420,73 +420,73 @@
         <v>24</v>
       </c>
       <c r="B2">
-        <v>0.00067031546302906637</v>
+        <v>0.0006691540271923555</v>
       </c>
       <c r="C2">
-        <v>0.0012234323848600858</v>
+        <v>0.0012234312212376765</v>
       </c>
       <c r="D2">
-        <v>1.4670984494697921e-05</v>
+        <v>1.4669868148521971e-05</v>
       </c>
       <c r="E2">
-        <v>-3.3500896723300891e-07</v>
+        <v>-3.3499323967960869e-07</v>
       </c>
       <c r="F2">
-        <v>-8.5144948177568114e-05</v>
+        <v>-8.514418116565512e-05</v>
       </c>
       <c r="G2">
-        <v>-0.00021652302968949811</v>
+        <v>-0.00021651781725157227</v>
       </c>
       <c r="H2">
-        <v>-7.2670120595454284e-05</v>
+        <v>-7.2676496969029182e-05</v>
       </c>
       <c r="I2">
-        <v>-0.00022637331280187206</v>
+        <v>-0.00022638279337677933</v>
       </c>
       <c r="J2">
-        <v>-0.0001214990104005733</v>
+        <v>-0.00012150450498448237</v>
       </c>
       <c r="K2">
-        <v>-0.00023581473125242172</v>
+        <v>-0.00023581320292812827</v>
       </c>
       <c r="L2">
-        <v>-0.00042887016546122006</v>
+        <v>-0.00042888195471345151</v>
       </c>
       <c r="M2">
-        <v>-0.00028644821741763659</v>
+        <v>-0.00028647655231701669</v>
       </c>
       <c r="N2">
-        <v>-0.00021378787544119957</v>
+        <v>-0.00021378693991043791</v>
       </c>
       <c r="O2">
-        <v>-0.00044611489383643348</v>
+        <v>-0.00044611502696220452</v>
       </c>
       <c r="P2">
-        <v>-0.00025007772098983047</v>
+        <v>-0.00025006872353346707</v>
       </c>
       <c r="Q2">
-        <v>-0.0002067953096925526</v>
+        <v>-0.00020679544211505254</v>
       </c>
       <c r="R2">
-        <v>-0.0002386334577069953</v>
+        <v>-0.00023864447035214272</v>
       </c>
       <c r="S2">
-        <v>-0.0001249379296789446</v>
+        <v>-0.00012493861360414799</v>
       </c>
       <c r="T2">
-        <v>5.7394359216633205e-05</v>
+        <v>5.7394808335676396e-05</v>
       </c>
       <c r="U2">
-        <v>-1.4625722378776959e-06</v>
+        <v>-1.4625903215741053e-06</v>
       </c>
       <c r="V2">
-        <v>-3.3936668521710248e-05</v>
+        <v>-3.3938422846402396e-05</v>
       </c>
       <c r="W2">
-        <v>-5.7896347274442997e-05</v>
+        <v>-5.7895343697502466e-05</v>
       </c>
       <c r="X2">
-        <v>-0.00071988674260084463</v>
+        <v>-0.00071986017024027946</v>
       </c>
     </row>
     <row r="3">
@@ -494,73 +494,73 @@
         <v>25</v>
       </c>
       <c r="B3">
-        <v>0.014190728000370655</v>
+        <v>0.014191204787707808</v>
       </c>
       <c r="C3">
-        <v>1.4670984494697921e-05</v>
+        <v>1.4669868148521971e-05</v>
       </c>
       <c r="D3">
-        <v>0.00075316929945348841</v>
+        <v>0.00075316896972869602</v>
       </c>
       <c r="E3">
-        <v>-1.2334606719160705e-05</v>
+        <v>-1.2334603868287213e-05</v>
       </c>
       <c r="F3">
-        <v>0.00021550064480034417</v>
+        <v>0.00021550188916998991</v>
       </c>
       <c r="G3">
-        <v>0.00023912164027871591</v>
+        <v>0.00023912549427157188</v>
       </c>
       <c r="H3">
-        <v>0.00096529897705421603</v>
+        <v>0.00096529786161566114</v>
       </c>
       <c r="I3">
-        <v>0.00051617421935350161</v>
+        <v>0.00051617460589646147</v>
       </c>
       <c r="J3">
-        <v>-7.9153133966512572e-05</v>
+        <v>-7.9151621293409476e-05</v>
       </c>
       <c r="K3">
-        <v>0.00038925903364898126</v>
+        <v>0.00038925838593994999</v>
       </c>
       <c r="L3">
-        <v>0.00042662875422445608</v>
+        <v>0.00042663177188269688</v>
       </c>
       <c r="M3">
-        <v>0.00052638654899815401</v>
+        <v>0.00052638173201890819</v>
       </c>
       <c r="N3">
-        <v>5.069801497772225e-05</v>
+        <v>5.0698000608349371e-05</v>
       </c>
       <c r="O3">
-        <v>-2.8300371211724754e-05</v>
+        <v>-2.8299989615481434e-05</v>
       </c>
       <c r="P3">
-        <v>-1.2157914507718304e-05</v>
+        <v>-1.2163438482169775e-05</v>
       </c>
       <c r="Q3">
-        <v>4.834843667387255e-06</v>
+        <v>4.8354368115382379e-06</v>
       </c>
       <c r="R3">
-        <v>0.00010512160776965547</v>
+        <v>0.00010511758577482269</v>
       </c>
       <c r="S3">
-        <v>9.7806052884669061e-05</v>
+        <v>9.7810087688839521e-05</v>
       </c>
       <c r="T3">
-        <v>0.00012822670475604904</v>
+        <v>0.00012822282780917613</v>
       </c>
       <c r="U3">
-        <v>-3.1160991750794735e-06</v>
+        <v>-3.1159961708303546e-06</v>
       </c>
       <c r="V3">
-        <v>6.8777034903890009e-05</v>
+        <v>6.8795521530521861e-05</v>
       </c>
       <c r="W3">
-        <v>5.0760675005927843e-05</v>
+        <v>5.0764331294595941e-05</v>
       </c>
       <c r="X3">
-        <v>-0.01299406356235619</v>
+        <v>-0.012994024759596448</v>
       </c>
     </row>
     <row r="4">
@@ -568,73 +568,73 @@
         <v>26</v>
       </c>
       <c r="B4">
-        <v>0.00094039710193433341</v>
+        <v>0.00094038855097516166</v>
       </c>
       <c r="C4">
-        <v>-3.3500896723300891e-07</v>
+        <v>-3.3499323967960869e-07</v>
       </c>
       <c r="D4">
-        <v>-1.2334606719160705e-05</v>
+        <v>-1.2334603868287213e-05</v>
       </c>
       <c r="E4">
-        <v>2.0469628229343481e-07</v>
+        <v>2.0469627963097525e-07</v>
       </c>
       <c r="F4">
-        <v>-3.3401231269607639e-06</v>
+        <v>-3.3401488855312521e-06</v>
       </c>
       <c r="G4">
-        <v>-3.9870545714160499e-06</v>
+        <v>-3.9871190487302237e-06</v>
       </c>
       <c r="H4">
-        <v>-1.4662543134864479e-05</v>
+        <v>-1.4662527983672973e-05</v>
       </c>
       <c r="I4">
-        <v>-8.2394636597226039e-06</v>
+        <v>-8.2394700052428808e-06</v>
       </c>
       <c r="J4">
-        <v>1.2983355304074337e-06</v>
+        <v>1.2983154209060012e-06</v>
       </c>
       <c r="K4">
-        <v>-6.0299467366284499e-06</v>
+        <v>-6.0299408483846407e-06</v>
       </c>
       <c r="L4">
-        <v>-6.6961301748707708e-06</v>
+        <v>-6.6961776410212538e-06</v>
       </c>
       <c r="M4">
-        <v>-8.4141406987507029e-06</v>
+        <v>-8.4140663166382883e-06</v>
       </c>
       <c r="N4">
-        <v>-6.2970944833130979e-07</v>
+        <v>-6.2970776373695125e-07</v>
       </c>
       <c r="O4">
-        <v>7.4946750017354481e-07</v>
+        <v>7.4946164250272397e-07</v>
       </c>
       <c r="P4">
-        <v>7.0252365118933302e-07</v>
+        <v>7.0260950129561313e-07</v>
       </c>
       <c r="Q4">
-        <v>2.9281992308659592e-07</v>
+        <v>2.9281157970790074e-07</v>
       </c>
       <c r="R4">
-        <v>-1.3767534503900422e-06</v>
+        <v>-1.3766830893643849e-06</v>
       </c>
       <c r="S4">
-        <v>-1.1985411161812999e-06</v>
+        <v>-1.1986034658602746e-06</v>
       </c>
       <c r="T4">
-        <v>-2.211182792666091e-06</v>
+        <v>-2.2111271768943239e-06</v>
       </c>
       <c r="U4">
-        <v>5.4084854896824453e-08</v>
+        <v>5.4083392637728923e-08</v>
       </c>
       <c r="V4">
-        <v>-1.1470442365969847e-06</v>
+        <v>-1.1473320086405721e-06</v>
       </c>
       <c r="W4">
-        <v>-7.9918909258955837e-07</v>
+        <v>-7.9924390415077263e-07</v>
       </c>
       <c r="X4">
-        <v>0.00021073224258589824</v>
+        <v>0.00021073170872462849</v>
       </c>
     </row>
     <row r="5">
@@ -642,73 +642,73 @@
         <v>27</v>
       </c>
       <c r="B5">
-        <v>-0.00023352579888884228</v>
+        <v>-0.00023619045116051222</v>
       </c>
       <c r="C5">
-        <v>-8.5144948177568114e-05</v>
+        <v>-8.514418116565512e-05</v>
       </c>
       <c r="D5">
-        <v>0.00021550064480034417</v>
+        <v>0.00021550188916998991</v>
       </c>
       <c r="E5">
-        <v>-3.3401231269607639e-06</v>
+        <v>-3.3401488855312521e-06</v>
       </c>
       <c r="F5">
-        <v>0.002099523653632356</v>
+        <v>0.0020995182973472131</v>
       </c>
       <c r="G5">
-        <v>0.00076956903763456517</v>
+        <v>0.00076956544336188285</v>
       </c>
       <c r="H5">
-        <v>0.00050622295151006884</v>
+        <v>0.00050621547653929182</v>
       </c>
       <c r="I5">
-        <v>-0.00027581660580009007</v>
+        <v>-0.000275826384741892</v>
       </c>
       <c r="J5">
-        <v>-0.0002241579125373649</v>
+        <v>-0.00022416155681528275</v>
       </c>
       <c r="K5">
-        <v>-0.00037298004321807639</v>
+        <v>-0.00037298349048661017</v>
       </c>
       <c r="L5">
-        <v>-0.00037688107646827038</v>
+        <v>-0.00037688994378195525</v>
       </c>
       <c r="M5">
-        <v>-0.00017134070476209769</v>
+        <v>-0.00017134266233243572</v>
       </c>
       <c r="N5">
-        <v>0.00024307427155070751</v>
+        <v>0.0002430728619064479</v>
       </c>
       <c r="O5">
-        <v>0.00027222534569370399</v>
+        <v>0.00027222137713292234</v>
       </c>
       <c r="P5">
-        <v>0.00010859748178982986</v>
+        <v>0.00010859396065741265</v>
       </c>
       <c r="Q5">
-        <v>0.00018876031685161922</v>
+        <v>0.00018875902385927386</v>
       </c>
       <c r="R5">
-        <v>0.00013268231175371842</v>
+        <v>0.00013268488981968971</v>
       </c>
       <c r="S5">
-        <v>0.00038001046591577608</v>
+        <v>0.0003800102323157469</v>
       </c>
       <c r="T5">
-        <v>9.5380910379544263e-06</v>
+        <v>9.5458129277679795e-06</v>
       </c>
       <c r="U5">
-        <v>-2.4759198650939324e-07</v>
+        <v>-2.4779592328197993e-07</v>
       </c>
       <c r="V5">
-        <v>-7.7177607945345104e-05</v>
+        <v>-7.7180305280802309e-05</v>
       </c>
       <c r="W5">
-        <v>-1.5566382281419363e-05</v>
+        <v>-1.5570360313795309e-05</v>
       </c>
       <c r="X5">
-        <v>-0.0040299053605443863</v>
+        <v>-0.0040299743959961339</v>
       </c>
     </row>
     <row r="6">
@@ -716,73 +716,73 @@
         <v>28</v>
       </c>
       <c r="B6">
-        <v>-0.040506424116675974</v>
+        <v>-0.040505999275069669</v>
       </c>
       <c r="C6">
-        <v>-0.00021652302968949811</v>
+        <v>-0.00021651781725157227</v>
       </c>
       <c r="D6">
-        <v>0.00023912164027871591</v>
+        <v>0.00023912549427157188</v>
       </c>
       <c r="E6">
-        <v>-3.9870545714160499e-06</v>
+        <v>-3.9871190487302237e-06</v>
       </c>
       <c r="F6">
-        <v>0.00076956903763456517</v>
+        <v>0.00076956544336188285</v>
       </c>
       <c r="G6">
-        <v>0.0017532647571415153</v>
+        <v>0.0017532680112295773</v>
       </c>
       <c r="H6">
-        <v>9.4223937835809929e-05</v>
+        <v>9.4220996939951493e-05</v>
       </c>
       <c r="I6">
-        <v>-0.00056112383596046433</v>
+        <v>-0.00056113303383792585</v>
       </c>
       <c r="J6">
-        <v>9.8780048884468006e-05</v>
+        <v>9.8775791629741525e-05</v>
       </c>
       <c r="K6">
-        <v>-0.00015697879623592081</v>
+        <v>-0.00015697745422757717</v>
       </c>
       <c r="L6">
-        <v>-0.00017227225603457799</v>
+        <v>-0.00017227218027823603</v>
       </c>
       <c r="M6">
-        <v>-4.0574491975690907e-05</v>
+        <v>-4.0562668478525527e-05</v>
       </c>
       <c r="N6">
-        <v>4.2647098313090999e-05</v>
+        <v>4.2647532156553456e-05</v>
       </c>
       <c r="O6">
-        <v>0.00018535311473860498</v>
+        <v>0.00018535194989153679</v>
       </c>
       <c r="P6">
-        <v>-5.6522467539587597e-05</v>
+        <v>-5.6527564742404543e-05</v>
       </c>
       <c r="Q6">
-        <v>-0.00019766119725852724</v>
+        <v>-0.00019766249395969555</v>
       </c>
       <c r="R6">
-        <v>-0.00019612675299998078</v>
+        <v>-0.00019612333935467883</v>
       </c>
       <c r="S6">
-        <v>-2.1466230038404708e-05</v>
+        <v>-2.1455633647065242e-05</v>
       </c>
       <c r="T6">
-        <v>-0.00010312133019312096</v>
+        <v>-0.00010310867324614219</v>
       </c>
       <c r="U6">
-        <v>3.0832572248803091e-06</v>
+        <v>3.082919824088867e-06</v>
       </c>
       <c r="V6">
-        <v>0.00030752307629658177</v>
+        <v>0.00030755277614396008</v>
       </c>
       <c r="W6">
-        <v>0.00021341875920975197</v>
+        <v>0.00021340940698398082</v>
       </c>
       <c r="X6">
-        <v>-0.0030191850748167055</v>
+        <v>-0.003019354599321511</v>
       </c>
     </row>
     <row r="7">
@@ -790,73 +790,73 @@
         <v>29</v>
       </c>
       <c r="B7">
-        <v>-0.017476233262360579</v>
+        <v>-0.017475201425518578</v>
       </c>
       <c r="C7">
-        <v>-7.2670120595454284e-05</v>
+        <v>-7.2676496969029182e-05</v>
       </c>
       <c r="D7">
-        <v>0.00096529897705421603</v>
+        <v>0.00096529786161566114</v>
       </c>
       <c r="E7">
-        <v>-1.4662543134864479e-05</v>
+        <v>-1.4662527983672973e-05</v>
       </c>
       <c r="F7">
-        <v>0.00050622295151006884</v>
+        <v>0.00050621547653929182</v>
       </c>
       <c r="G7">
-        <v>9.4223937835809929e-05</v>
+        <v>9.4220996939951493e-05</v>
       </c>
       <c r="H7">
-        <v>0.0067546436862631586</v>
+        <v>0.0067546484565675202</v>
       </c>
       <c r="I7">
-        <v>0.004599316335438937</v>
+        <v>0.0045993246543285637</v>
       </c>
       <c r="J7">
-        <v>-0.000251090837295612</v>
+        <v>-0.00025109329655357508</v>
       </c>
       <c r="K7">
-        <v>0.0035826657843480579</v>
+        <v>0.0035826679847354918</v>
       </c>
       <c r="L7">
-        <v>0.0044361203347076487</v>
+        <v>0.0044361260610234817</v>
       </c>
       <c r="M7">
-        <v>0.0044388257921594435</v>
+        <v>0.0044388297271491014</v>
       </c>
       <c r="N7">
-        <v>0.0005276423250174505</v>
+        <v>0.00052764686844024127</v>
       </c>
       <c r="O7">
-        <v>-0.00020059890022057665</v>
+        <v>-0.0002005975173697324</v>
       </c>
       <c r="P7">
-        <v>5.0808859393986806e-05</v>
+        <v>5.0821662436838395e-05</v>
       </c>
       <c r="Q7">
-        <v>0.00025088623145139676</v>
+        <v>0.00025089081220086833</v>
       </c>
       <c r="R7">
-        <v>0.00028059114536838645</v>
+        <v>0.00028059474512940328</v>
       </c>
       <c r="S7">
-        <v>0.00050869103288752378</v>
+        <v>0.00050869178156869683</v>
       </c>
       <c r="T7">
-        <v>-1.0531834735817182e-05</v>
+        <v>-1.0525368963917522e-05</v>
       </c>
       <c r="U7">
-        <v>1.5946930852112648e-06</v>
+        <v>1.5945043417644762e-06</v>
       </c>
       <c r="V7">
-        <v>0.00030430181189942951</v>
+        <v>0.000304289422942596</v>
       </c>
       <c r="W7">
-        <v>0.00032414463242732595</v>
+        <v>0.00032413422547955192</v>
       </c>
       <c r="X7">
-        <v>-0.020722066198303066</v>
+        <v>-0.020722099993364121</v>
       </c>
     </row>
     <row r="8">
@@ -864,73 +864,73 @@
         <v>30</v>
       </c>
       <c r="B8">
-        <v>0.063934954090616822</v>
+        <v>0.063937475399824639</v>
       </c>
       <c r="C8">
-        <v>-0.00022637331280187206</v>
+        <v>-0.00022638279337677933</v>
       </c>
       <c r="D8">
-        <v>0.00051617421935350161</v>
+        <v>0.00051617460589646147</v>
       </c>
       <c r="E8">
-        <v>-8.2394636597226039e-06</v>
+        <v>-8.2394700052428808e-06</v>
       </c>
       <c r="F8">
-        <v>-0.00027581660580009007</v>
+        <v>-0.000275826384741892</v>
       </c>
       <c r="G8">
-        <v>-0.00056112383596046433</v>
+        <v>-0.00056113303383792585</v>
       </c>
       <c r="H8">
-        <v>0.004599316335438937</v>
+        <v>0.0045993246543285637</v>
       </c>
       <c r="I8">
-        <v>0.0064283012192306527</v>
+        <v>0.0064283148073547916</v>
       </c>
       <c r="J8">
-        <v>0.0005204047907230861</v>
+        <v>0.00052040450937110077</v>
       </c>
       <c r="K8">
-        <v>0.0046556446861280359</v>
+        <v>0.0046556485770633026</v>
       </c>
       <c r="L8">
-        <v>0.0056122097689550818</v>
+        <v>0.0056122161707406193</v>
       </c>
       <c r="M8">
-        <v>0.0055511547283043725</v>
+        <v>0.0055511599359951069</v>
       </c>
       <c r="N8">
-        <v>0.00060661168876749005</v>
+        <v>0.00060661506740796768</v>
       </c>
       <c r="O8">
-        <v>-0.00010351411687909481</v>
+        <v>-0.00010351475397745672</v>
       </c>
       <c r="P8">
-        <v>4.4092336656645185e-05</v>
+        <v>4.4105059050825873e-05</v>
       </c>
       <c r="Q8">
-        <v>0.00041848757415268584</v>
+        <v>0.00041848833410669355</v>
       </c>
       <c r="R8">
-        <v>0.00049701068144264839</v>
+        <v>0.00049701679275710234</v>
       </c>
       <c r="S8">
-        <v>7.7052509722586385e-05</v>
+        <v>7.704520214242192e-05</v>
       </c>
       <c r="T8">
-        <v>5.6242278751155589e-05</v>
+        <v>5.6242007746657233e-05</v>
       </c>
       <c r="U8">
-        <v>1.2974849833140181e-07</v>
+        <v>1.2973634851704409e-07</v>
       </c>
       <c r="V8">
-        <v>-1.5122510281339978e-05</v>
+        <v>-1.5156171756740017e-05</v>
       </c>
       <c r="W8">
-        <v>0.00028354475444172843</v>
+        <v>0.00028353766856027327</v>
       </c>
       <c r="X8">
-        <v>-0.014595033450607559</v>
+        <v>-0.014595027911356577</v>
       </c>
     </row>
     <row r="9">
@@ -938,73 +938,73 @@
         <v>31</v>
       </c>
       <c r="B9">
-        <v>0.03089609537906287</v>
+        <v>0.030897434925785172</v>
       </c>
       <c r="C9">
-        <v>-0.0001214990104005733</v>
+        <v>-0.00012150450498448237</v>
       </c>
       <c r="D9">
-        <v>-7.9153133966512572e-05</v>
+        <v>-7.9151621293409476e-05</v>
       </c>
       <c r="E9">
-        <v>1.2983355304074337e-06</v>
+        <v>1.2983154209060012e-06</v>
       </c>
       <c r="F9">
-        <v>-0.0002241579125373649</v>
+        <v>-0.00022416155681528275</v>
       </c>
       <c r="G9">
-        <v>9.8780048884468006e-05</v>
+        <v>9.8775791629741525e-05</v>
       </c>
       <c r="H9">
-        <v>-0.000251090837295612</v>
+        <v>-0.00025109329655357508</v>
       </c>
       <c r="I9">
-        <v>0.0005204047907230861</v>
+        <v>0.00052040450937110077</v>
       </c>
       <c r="J9">
-        <v>0.002962587162795753</v>
+        <v>0.0029625879101285685</v>
       </c>
       <c r="K9">
-        <v>0.0018675268753238438</v>
+        <v>0.0018675283156046987</v>
       </c>
       <c r="L9">
-        <v>0.0019295407688982959</v>
+        <v>0.0019295393555241876</v>
       </c>
       <c r="M9">
-        <v>0.0018814470881972096</v>
+        <v>0.001881446829043852</v>
       </c>
       <c r="N9">
-        <v>-6.86127242373177e-05</v>
+        <v>-6.8613544504253238e-05</v>
       </c>
       <c r="O9">
-        <v>-4.4667102912822332e-05</v>
+        <v>-4.4669134216694835e-05</v>
       </c>
       <c r="P9">
-        <v>0.00012506050577644763</v>
+        <v>0.00012506335400606485</v>
       </c>
       <c r="Q9">
-        <v>-9.0768116152918524e-05</v>
+        <v>-9.0769342035093483e-05</v>
       </c>
       <c r="R9">
-        <v>-0.00016727630470777564</v>
+        <v>-0.00016727071742877878</v>
       </c>
       <c r="S9">
-        <v>-0.00027042961372206496</v>
+        <v>-0.00027043139137982044</v>
       </c>
       <c r="T9">
-        <v>-9.6125702010555012e-05</v>
+        <v>-9.6135058073166298e-05</v>
       </c>
       <c r="U9">
-        <v>2.9446519803338951e-06</v>
+        <v>2.9449056855750877e-06</v>
       </c>
       <c r="V9">
-        <v>0.00016281705851138622</v>
+        <v>0.00016283026149205814</v>
       </c>
       <c r="W9">
-        <v>0.00019480973464896791</v>
+        <v>0.00019481291438440613</v>
       </c>
       <c r="X9">
-        <v>0.00017159367223051544</v>
+        <v>0.00017165430327413782</v>
       </c>
     </row>
     <row r="10">
@@ -1012,73 +1012,73 @@
         <v>32</v>
       </c>
       <c r="B10">
-        <v>0.13631641253914301</v>
+        <v>0.13631486342071</v>
       </c>
       <c r="C10">
-        <v>-0.00023581473125242172</v>
+        <v>-0.00023581320292812827</v>
       </c>
       <c r="D10">
-        <v>0.00038925903364898126</v>
+        <v>0.00038925838593994999</v>
       </c>
       <c r="E10">
-        <v>-6.0299467366284499e-06</v>
+        <v>-6.0299408483846407e-06</v>
       </c>
       <c r="F10">
-        <v>-0.00037298004321807639</v>
+        <v>-0.00037298349048661017</v>
       </c>
       <c r="G10">
-        <v>-0.00015697879623592081</v>
+        <v>-0.00015697745422757717</v>
       </c>
       <c r="H10">
-        <v>0.0035826657843480579</v>
+        <v>0.0035826679847354918</v>
       </c>
       <c r="I10">
-        <v>0.0046556446861280359</v>
+        <v>0.0046556485770633026</v>
       </c>
       <c r="J10">
-        <v>0.0018675268753238438</v>
+        <v>0.0018675283156046987</v>
       </c>
       <c r="K10">
-        <v>0.0064502076769358974</v>
+        <v>0.0064502192139104441</v>
       </c>
       <c r="L10">
-        <v>0.0056575958306886191</v>
+        <v>0.0056576022561494206</v>
       </c>
       <c r="M10">
-        <v>0.005570305884708548</v>
+        <v>0.0055703160817910857</v>
       </c>
       <c r="N10">
-        <v>0.00046642530780603968</v>
+        <v>0.00046642632484625909</v>
       </c>
       <c r="O10">
-        <v>8.3614105741911839e-05</v>
+        <v>8.3611895622163167e-05</v>
       </c>
       <c r="P10">
-        <v>4.5346759605819145e-05</v>
+        <v>4.5340411373484806e-05</v>
       </c>
       <c r="Q10">
-        <v>0.00029938083457872831</v>
+        <v>0.00029938065381596504</v>
       </c>
       <c r="R10">
-        <v>0.00038716646227804168</v>
+        <v>0.00038717046331863519</v>
       </c>
       <c r="S10">
-        <v>6.0742559887387668e-05</v>
+        <v>6.0746501642556248e-05</v>
       </c>
       <c r="T10">
-        <v>-8.8218911630923678e-05</v>
+        <v>-8.8225367978157429e-05</v>
       </c>
       <c r="U10">
-        <v>3.1613170862366136e-06</v>
+        <v>3.1614972443156611e-06</v>
       </c>
       <c r="V10">
-        <v>0.00066412649706449234</v>
+        <v>0.00066415493360393106</v>
       </c>
       <c r="W10">
-        <v>0.00045098363341509475</v>
+        <v>0.0004509843284580047</v>
       </c>
       <c r="X10">
-        <v>-0.011377583552645898</v>
+        <v>-0.011377525304068124</v>
       </c>
     </row>
     <row r="11">
@@ -1086,73 +1086,73 @@
         <v>33</v>
       </c>
       <c r="B11">
-        <v>0.20447311286941655</v>
+        <v>0.20447422837802501</v>
       </c>
       <c r="C11">
-        <v>-0.00042887016546122006</v>
+        <v>-0.00042888195471345151</v>
       </c>
       <c r="D11">
-        <v>0.00042662875422445608</v>
+        <v>0.00042663177188269688</v>
       </c>
       <c r="E11">
-        <v>-6.6961301748707708e-06</v>
+        <v>-6.6961776410212538e-06</v>
       </c>
       <c r="F11">
-        <v>-0.00037688107646827038</v>
+        <v>-0.00037688994378195525</v>
       </c>
       <c r="G11">
-        <v>-0.00017227225603457799</v>
+        <v>-0.00017227218027823603</v>
       </c>
       <c r="H11">
-        <v>0.0044361203347076487</v>
+        <v>0.0044361260610234817</v>
       </c>
       <c r="I11">
-        <v>0.0056122097689550818</v>
+        <v>0.0056122161707406193</v>
       </c>
       <c r="J11">
-        <v>0.0019295407688982959</v>
+        <v>0.0019295393555241876</v>
       </c>
       <c r="K11">
-        <v>0.0056575958306886191</v>
+        <v>0.0056576022561494206</v>
       </c>
       <c r="L11">
-        <v>0.0076004024450885555</v>
+        <v>0.0076004122085402536</v>
       </c>
       <c r="M11">
-        <v>0.006481040079620983</v>
+        <v>0.0064810510374092162</v>
       </c>
       <c r="N11">
-        <v>0.00033943769253768665</v>
+        <v>0.00033943992150123944</v>
       </c>
       <c r="O11">
-        <v>-0.00033927861376061193</v>
+        <v>-0.00033928301937210994</v>
       </c>
       <c r="P11">
-        <v>-0.0002055955747221421</v>
+        <v>-0.00020558109344744058</v>
       </c>
       <c r="Q11">
-        <v>0.00011510446370832303</v>
+        <v>0.00011510323199812478</v>
       </c>
       <c r="R11">
-        <v>8.3630313227906351e-05</v>
+        <v>8.3635695953165955e-05</v>
       </c>
       <c r="S11">
-        <v>-3.2985462097512297e-05</v>
+        <v>-3.2987334583646759e-05</v>
       </c>
       <c r="T11">
-        <v>8.9686869188922505e-06</v>
+        <v>8.9718380849070079e-06</v>
       </c>
       <c r="U11">
-        <v>1.4273821014347467e-06</v>
+        <v>1.4272829273948083e-06</v>
       </c>
       <c r="V11">
-        <v>0.00029651833547903383</v>
+        <v>0.0002965231179308421</v>
       </c>
       <c r="W11">
-        <v>0.00042203502081150342</v>
+        <v>0.00042202505415091544</v>
       </c>
       <c r="X11">
-        <v>-0.013588985962256349</v>
+        <v>-0.013589054405601798</v>
       </c>
     </row>
     <row r="12">
@@ -1160,73 +1160,73 @@
         <v>34</v>
       </c>
       <c r="B12">
-        <v>0.26801601511174761</v>
+        <v>0.26801440015636496</v>
       </c>
       <c r="C12">
-        <v>-0.00028644821741763659</v>
+        <v>-0.00028647655231701669</v>
       </c>
       <c r="D12">
-        <v>0.00052638654899815401</v>
+        <v>0.00052638173201890819</v>
       </c>
       <c r="E12">
-        <v>-8.4141406987507029e-06</v>
+        <v>-8.4140663166382883e-06</v>
       </c>
       <c r="F12">
-        <v>-0.00017134070476209769</v>
+        <v>-0.00017134266233243572</v>
       </c>
       <c r="G12">
-        <v>-4.0574491975690907e-05</v>
+        <v>-4.0562668478525527e-05</v>
       </c>
       <c r="H12">
-        <v>0.0044388257921594435</v>
+        <v>0.0044388297271491014</v>
       </c>
       <c r="I12">
-        <v>0.0055511547283043725</v>
+        <v>0.0055511599359951069</v>
       </c>
       <c r="J12">
-        <v>0.0018814470881972096</v>
+        <v>0.001881446829043852</v>
       </c>
       <c r="K12">
-        <v>0.005570305884708548</v>
+        <v>0.0055703160817910857</v>
       </c>
       <c r="L12">
-        <v>0.006481040079620983</v>
+        <v>0.0064810510374092162</v>
       </c>
       <c r="M12">
-        <v>0.0089540914672575477</v>
+        <v>0.0089540341657703623</v>
       </c>
       <c r="N12">
-        <v>0.0002980937756598967</v>
+        <v>0.00029809990611835528</v>
       </c>
       <c r="O12">
-        <v>-0.00048247070908506197</v>
+        <v>-0.00048245539372169816</v>
       </c>
       <c r="P12">
-        <v>-0.00039255416167624947</v>
+        <v>-0.00039253972396190813</v>
       </c>
       <c r="Q12">
-        <v>9.2167893322333411e-05</v>
+        <v>9.2172585887501449e-05</v>
       </c>
       <c r="R12">
-        <v>0.00037771794569394998</v>
+        <v>0.00037769281730120317</v>
       </c>
       <c r="S12">
-        <v>-9.5577430037732322e-05</v>
+        <v>-9.5581922981158481e-05</v>
       </c>
       <c r="T12">
-        <v>0.00019816916086114449</v>
+        <v>0.00019814353422234129</v>
       </c>
       <c r="U12">
-        <v>-3.4100503994572004e-06</v>
+        <v>-3.4093718161446124e-06</v>
       </c>
       <c r="V12">
-        <v>0.000274679092421036</v>
+        <v>0.00027469680377451098</v>
       </c>
       <c r="W12">
-        <v>0.0004251835490145029</v>
+        <v>0.00042520346007512153</v>
       </c>
       <c r="X12">
-        <v>-0.016825164866262482</v>
+        <v>-0.016824856430950185</v>
       </c>
     </row>
     <row r="13">
@@ -1234,73 +1234,73 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>0.062307614379080951</v>
+        <v>0.062309783137965105</v>
       </c>
       <c r="C13">
-        <v>-0.00021378787544119957</v>
+        <v>-0.00021378693991043791</v>
       </c>
       <c r="D13">
-        <v>5.069801497772225e-05</v>
+        <v>5.0698000608349371e-05</v>
       </c>
       <c r="E13">
-        <v>-6.2970944833130979e-07</v>
+        <v>-6.2970776373695125e-07</v>
       </c>
       <c r="F13">
-        <v>0.00024307427155070751</v>
+        <v>0.0002430728619064479</v>
       </c>
       <c r="G13">
-        <v>4.2647098313090999e-05</v>
+        <v>4.2647532156553456e-05</v>
       </c>
       <c r="H13">
-        <v>0.0005276423250174505</v>
+        <v>0.00052764686844024127</v>
       </c>
       <c r="I13">
-        <v>0.00060661168876749005</v>
+        <v>0.00060661506740796768</v>
       </c>
       <c r="J13">
-        <v>-6.86127242373177e-05</v>
+        <v>-6.8613544504253238e-05</v>
       </c>
       <c r="K13">
-        <v>0.00046642530780603968</v>
+        <v>0.00046642632484625909</v>
       </c>
       <c r="L13">
-        <v>0.00033943769253768665</v>
+        <v>0.00033943992150123944</v>
       </c>
       <c r="M13">
-        <v>0.0002980937756598967</v>
+        <v>0.00029809990611835528</v>
       </c>
       <c r="N13">
-        <v>0.0079062067867891675</v>
+        <v>0.0079062224042226858</v>
       </c>
       <c r="O13">
-        <v>0.0060832000566064179</v>
+        <v>0.0060832147066223795</v>
       </c>
       <c r="P13">
-        <v>0.0060329545769424609</v>
+        <v>0.0060329687347993408</v>
       </c>
       <c r="Q13">
-        <v>0.0060599242564253527</v>
+        <v>0.0060599395698174219</v>
       </c>
       <c r="R13">
-        <v>0.0060284482414423675</v>
+        <v>0.0060284651498919463</v>
       </c>
       <c r="S13">
-        <v>0.0060461221212694842</v>
+        <v>0.0060461377633265322</v>
       </c>
       <c r="T13">
-        <v>-0.00013475877993701689</v>
+        <v>-0.00013475580198615746</v>
       </c>
       <c r="U13">
-        <v>4.0985624615884678e-06</v>
+        <v>4.0984826773624619e-06</v>
       </c>
       <c r="V13">
-        <v>8.9410873700590445e-06</v>
+        <v>8.9397652560736958e-06</v>
       </c>
       <c r="W13">
-        <v>0.00019487591678812052</v>
+        <v>0.00019487508370256979</v>
       </c>
       <c r="X13">
-        <v>-0.0063563241374388312</v>
+        <v>-0.0063563702091149338</v>
       </c>
     </row>
     <row r="14">
@@ -1308,73 +1308,73 @@
         <v>36</v>
       </c>
       <c r="B14">
-        <v>0.095064625954040222</v>
+        <v>0.095061204651987627</v>
       </c>
       <c r="C14">
-        <v>-0.00044611489383643348</v>
+        <v>-0.00044611502696220452</v>
       </c>
       <c r="D14">
-        <v>-2.8300371211724754e-05</v>
+        <v>-2.8299989615481434e-05</v>
       </c>
       <c r="E14">
-        <v>7.4946750017354481e-07</v>
+        <v>7.4946164250272397e-07</v>
       </c>
       <c r="F14">
-        <v>0.00027222534569370399</v>
+        <v>0.00027222137713292234</v>
       </c>
       <c r="G14">
-        <v>0.00018535311473860498</v>
+        <v>0.00018535194989153679</v>
       </c>
       <c r="H14">
-        <v>-0.00020059890022057665</v>
+        <v>-0.0002005975173697324</v>
       </c>
       <c r="I14">
-        <v>-0.00010351411687909481</v>
+        <v>-0.00010351475397745672</v>
       </c>
       <c r="J14">
-        <v>-4.4667102912822332e-05</v>
+        <v>-4.4669134216694835e-05</v>
       </c>
       <c r="K14">
-        <v>8.3614105741911839e-05</v>
+        <v>8.3611895622163167e-05</v>
       </c>
       <c r="L14">
-        <v>-0.00033927861376061193</v>
+        <v>-0.00033928301937210994</v>
       </c>
       <c r="M14">
-        <v>-0.00048247070908506197</v>
+        <v>-0.00048245539372169816</v>
       </c>
       <c r="N14">
-        <v>0.0060832000566064179</v>
+        <v>0.0060832147066223795</v>
       </c>
       <c r="O14">
-        <v>0.0083957094904278627</v>
+        <v>0.0083957325185063068</v>
       </c>
       <c r="P14">
-        <v>0.0061092939816440829</v>
+        <v>0.0061093071353620528</v>
       </c>
       <c r="Q14">
-        <v>0.0060891114996909626</v>
+        <v>0.0060891258568868539</v>
       </c>
       <c r="R14">
-        <v>0.0060227868393965909</v>
+        <v>0.0060228079270150401</v>
       </c>
       <c r="S14">
-        <v>0.0060777230663468049</v>
+        <v>0.006077739739748355</v>
       </c>
       <c r="T14">
-        <v>-0.00023726867942062057</v>
+        <v>-0.00023726552909100469</v>
       </c>
       <c r="U14">
-        <v>6.5815820905024979e-06</v>
+        <v>6.581508386615578e-06</v>
       </c>
       <c r="V14">
-        <v>6.1142790614286853e-06</v>
+        <v>6.1177803449144821e-06</v>
       </c>
       <c r="W14">
-        <v>0.00026289092223410939</v>
+        <v>0.00026288953207990876</v>
       </c>
       <c r="X14">
-        <v>-0.0035611039623777846</v>
+        <v>-0.0035611540773963085</v>
       </c>
     </row>
     <row r="15">
@@ -1382,73 +1382,73 @@
         <v>37</v>
       </c>
       <c r="B15">
-        <v>0.043345627515009401</v>
+        <v>0.043348354726689568</v>
       </c>
       <c r="C15">
-        <v>-0.00025007772098983047</v>
+        <v>-0.00025006872353346707</v>
       </c>
       <c r="D15">
-        <v>-1.2157914507718304e-05</v>
+        <v>-1.2163438482169775e-05</v>
       </c>
       <c r="E15">
-        <v>7.0252365118933302e-07</v>
+        <v>7.0260950129561313e-07</v>
       </c>
       <c r="F15">
-        <v>0.00010859748178982986</v>
+        <v>0.00010859396065741265</v>
       </c>
       <c r="G15">
-        <v>-5.6522467539587597e-05</v>
+        <v>-5.6527564742404543e-05</v>
       </c>
       <c r="H15">
-        <v>5.0808859393986806e-05</v>
+        <v>5.0821662436838395e-05</v>
       </c>
       <c r="I15">
-        <v>4.4092336656645185e-05</v>
+        <v>4.4105059050825873e-05</v>
       </c>
       <c r="J15">
-        <v>0.00012506050577644763</v>
+        <v>0.00012506335400606485</v>
       </c>
       <c r="K15">
-        <v>4.5346759605819145e-05</v>
+        <v>4.5340411373484806e-05</v>
       </c>
       <c r="L15">
-        <v>-0.0002055955747221421</v>
+        <v>-0.00020558109344744058</v>
       </c>
       <c r="M15">
-        <v>-0.00039255416167624947</v>
+        <v>-0.00039253972396190813</v>
       </c>
       <c r="N15">
-        <v>0.0060329545769424609</v>
+        <v>0.0060329687347993408</v>
       </c>
       <c r="O15">
-        <v>0.0061092939816440829</v>
+        <v>0.0061093071353620528</v>
       </c>
       <c r="P15">
-        <v>0.0080748238618788392</v>
+        <v>0.0080748113456463513</v>
       </c>
       <c r="Q15">
-        <v>0.0060747919174767582</v>
+        <v>0.0060748062824215717</v>
       </c>
       <c r="R15">
-        <v>0.0060309915067183976</v>
+        <v>0.0060310099561455954</v>
       </c>
       <c r="S15">
-        <v>0.0060699523063027791</v>
+        <v>0.0060699682342559083</v>
       </c>
       <c r="T15">
-        <v>-0.0002223099108256796</v>
+        <v>-0.00022232402094960217</v>
       </c>
       <c r="U15">
-        <v>5.8361982959960341e-06</v>
+        <v>5.8366217142982716e-06</v>
       </c>
       <c r="V15">
-        <v>-5.9022521819152712e-05</v>
+        <v>-5.9006254171960291e-05</v>
       </c>
       <c r="W15">
-        <v>0.00010752368533522964</v>
+        <v>0.00010753854138199751</v>
       </c>
       <c r="X15">
-        <v>-0.0041223395296215576</v>
+        <v>-0.004122174778308986</v>
       </c>
     </row>
     <row r="16">
@@ -1456,73 +1456,73 @@
         <v>38</v>
       </c>
       <c r="B16">
-        <v>0.1015430072209776</v>
+        <v>0.10154441154303673</v>
       </c>
       <c r="C16">
-        <v>-0.0002067953096925526</v>
+        <v>-0.00020679544211505254</v>
       </c>
       <c r="D16">
-        <v>4.834843667387255e-06</v>
+        <v>4.8354368115382379e-06</v>
       </c>
       <c r="E16">
-        <v>2.9281992308659592e-07</v>
+        <v>2.9281157970790074e-07</v>
       </c>
       <c r="F16">
-        <v>0.00018876031685161922</v>
+        <v>0.00018875902385927386</v>
       </c>
       <c r="G16">
-        <v>-0.00019766119725852724</v>
+        <v>-0.00019766249395969555</v>
       </c>
       <c r="H16">
-        <v>0.00025088623145139676</v>
+        <v>0.00025089081220086833</v>
       </c>
       <c r="I16">
-        <v>0.00041848757415268584</v>
+        <v>0.00041848833410669355</v>
       </c>
       <c r="J16">
-        <v>-9.0768116152918524e-05</v>
+        <v>-9.0769342035093483e-05</v>
       </c>
       <c r="K16">
-        <v>0.00029938083457872831</v>
+        <v>0.00029938065381596504</v>
       </c>
       <c r="L16">
-        <v>0.00011510446370832303</v>
+        <v>0.00011510323199812478</v>
       </c>
       <c r="M16">
-        <v>9.2167893322333411e-05</v>
+        <v>9.2172585887501449e-05</v>
       </c>
       <c r="N16">
-        <v>0.0060599242564253527</v>
+        <v>0.0060599395698174219</v>
       </c>
       <c r="O16">
-        <v>0.0060891114996909626</v>
+        <v>0.0060891258568868539</v>
       </c>
       <c r="P16">
-        <v>0.0060747919174767582</v>
+        <v>0.0060748062824215717</v>
       </c>
       <c r="Q16">
-        <v>0.0077660944413879864</v>
+        <v>0.0077661107850402807</v>
       </c>
       <c r="R16">
-        <v>0.0060776908529996598</v>
+        <v>0.0060777083624356677</v>
       </c>
       <c r="S16">
-        <v>0.0060983356490135789</v>
+        <v>0.0060983512364471398</v>
       </c>
       <c r="T16">
-        <v>-0.00017545685128278954</v>
+        <v>-0.00017545425546831969</v>
       </c>
       <c r="U16">
-        <v>4.9997948275196962e-06</v>
+        <v>4.9997249209014281e-06</v>
       </c>
       <c r="V16">
-        <v>-0.0001536030148505355</v>
+        <v>-0.00015360392109117554</v>
       </c>
       <c r="W16">
-        <v>9.4302004474083856e-05</v>
+        <v>9.4301582570887558e-05</v>
       </c>
       <c r="X16">
-        <v>-0.0051179308176552522</v>
+        <v>-0.0051179788735218612</v>
       </c>
     </row>
     <row r="17">
@@ -1530,73 +1530,73 @@
         <v>39</v>
       </c>
       <c r="B17">
-        <v>0.047836046331134953</v>
+        <v>0.047838733048040601</v>
       </c>
       <c r="C17">
-        <v>-0.0002386334577069953</v>
+        <v>-0.00023864447035214272</v>
       </c>
       <c r="D17">
-        <v>0.00010512160776965547</v>
+        <v>0.00010511758577482269</v>
       </c>
       <c r="E17">
-        <v>-1.3767534503900422e-06</v>
+        <v>-1.3766830893643849e-06</v>
       </c>
       <c r="F17">
-        <v>0.00013268231175371842</v>
+        <v>0.00013268488981968971</v>
       </c>
       <c r="G17">
-        <v>-0.00019612675299998078</v>
+        <v>-0.00019612333935467883</v>
       </c>
       <c r="H17">
-        <v>0.00028059114536838645</v>
+        <v>0.00028059474512940328</v>
       </c>
       <c r="I17">
-        <v>0.00049701068144264839</v>
+        <v>0.00049701679275710234</v>
       </c>
       <c r="J17">
-        <v>-0.00016727630470777564</v>
+        <v>-0.00016727071742877878</v>
       </c>
       <c r="K17">
-        <v>0.00038716646227804168</v>
+        <v>0.00038717046331863519</v>
       </c>
       <c r="L17">
-        <v>8.3630313227906351e-05</v>
+        <v>8.3635695953165955e-05</v>
       </c>
       <c r="M17">
-        <v>0.00037771794569394998</v>
+        <v>0.00037769281730120317</v>
       </c>
       <c r="N17">
-        <v>0.0060284482414423675</v>
+        <v>0.0060284651498919463</v>
       </c>
       <c r="O17">
-        <v>0.0060227868393965909</v>
+        <v>0.0060228079270150401</v>
       </c>
       <c r="P17">
-        <v>0.0060309915067183976</v>
+        <v>0.0060310099561455954</v>
       </c>
       <c r="Q17">
-        <v>0.0060776908529996598</v>
+        <v>0.0060777083624356677</v>
       </c>
       <c r="R17">
-        <v>0.0073275748487816048</v>
+        <v>0.0073275801313488279</v>
       </c>
       <c r="S17">
-        <v>0.0060798176173210671</v>
+        <v>0.0060798340173464699</v>
       </c>
       <c r="T17">
-        <v>-7.5717247819548621e-05</v>
+        <v>-7.5732908092537594e-05</v>
       </c>
       <c r="U17">
-        <v>2.0100475070293733e-06</v>
+        <v>2.0104623675935016e-06</v>
       </c>
       <c r="V17">
-        <v>-0.00014850496720077177</v>
+        <v>-0.00014849576739575806</v>
       </c>
       <c r="W17">
-        <v>-1.5778325103062239e-05</v>
+        <v>-1.5764205119582486e-05</v>
       </c>
       <c r="X17">
-        <v>-0.0073301867145243657</v>
+        <v>-0.0073300090817103175</v>
       </c>
     </row>
     <row r="18">
@@ -1604,73 +1604,73 @@
         <v>40</v>
       </c>
       <c r="B18">
-        <v>0.098188810765327636</v>
+        <v>0.098192927714609857</v>
       </c>
       <c r="C18">
-        <v>-0.0001249379296789446</v>
+        <v>-0.00012493861360414799</v>
       </c>
       <c r="D18">
-        <v>9.7806052884669061e-05</v>
+        <v>9.7810087688839521e-05</v>
       </c>
       <c r="E18">
-        <v>-1.1985411161812999e-06</v>
+        <v>-1.1986034658602746e-06</v>
       </c>
       <c r="F18">
-        <v>0.00038001046591577608</v>
+        <v>0.0003800102323157469</v>
       </c>
       <c r="G18">
-        <v>-2.1466230038404708e-05</v>
+        <v>-2.1455633647065242e-05</v>
       </c>
       <c r="H18">
-        <v>0.00050869103288752378</v>
+        <v>0.00050869178156869683</v>
       </c>
       <c r="I18">
-        <v>7.7052509722586385e-05</v>
+        <v>7.704520214242192e-05</v>
       </c>
       <c r="J18">
-        <v>-0.00027042961372206496</v>
+        <v>-0.00027043139137982044</v>
       </c>
       <c r="K18">
-        <v>6.0742559887387668e-05</v>
+        <v>6.0746501642556248e-05</v>
       </c>
       <c r="L18">
-        <v>-3.2985462097512297e-05</v>
+        <v>-3.2987334583646759e-05</v>
       </c>
       <c r="M18">
-        <v>-9.5577430037732322e-05</v>
+        <v>-9.5581922981158481e-05</v>
       </c>
       <c r="N18">
-        <v>0.0060461221212694842</v>
+        <v>0.0060461377633265322</v>
       </c>
       <c r="O18">
-        <v>0.0060777230663468049</v>
+        <v>0.006077739739748355</v>
       </c>
       <c r="P18">
-        <v>0.0060699523063027791</v>
+        <v>0.0060699682342559083</v>
       </c>
       <c r="Q18">
-        <v>0.0060983356490135789</v>
+        <v>0.0060983512364471398</v>
       </c>
       <c r="R18">
-        <v>0.0060798176173210671</v>
+        <v>0.0060798340173464699</v>
       </c>
       <c r="S18">
-        <v>0.0075939096845849567</v>
+        <v>0.0075939321670416308</v>
       </c>
       <c r="T18">
-        <v>6.8027077843045396e-05</v>
+        <v>6.8029409632777618e-05</v>
       </c>
       <c r="U18">
-        <v>-2.1484180467304457e-06</v>
+        <v>-2.1484853374178993e-06</v>
       </c>
       <c r="V18">
-        <v>6.7819932254616815e-05</v>
+        <v>6.7861140385467797e-05</v>
       </c>
       <c r="W18">
-        <v>-8.0915305141382194e-05</v>
+        <v>-8.0915287765655035e-05</v>
       </c>
       <c r="X18">
-        <v>-0.0083973349829026753</v>
+        <v>-0.0083974354665247476</v>
       </c>
     </row>
     <row r="19">
@@ -1678,73 +1678,73 @@
         <v>41</v>
       </c>
       <c r="B19">
-        <v>-0.048528485279940074</v>
+        <v>-0.048532275959644856</v>
       </c>
       <c r="C19">
-        <v>5.7394359216633205e-05</v>
+        <v>5.7394808335676396e-05</v>
       </c>
       <c r="D19">
-        <v>0.00012822670475604904</v>
+        <v>0.00012822282780917613</v>
       </c>
       <c r="E19">
-        <v>-2.211182792666091e-06</v>
+        <v>-2.2111271768943239e-06</v>
       </c>
       <c r="F19">
-        <v>9.5380910379544263e-06</v>
+        <v>9.5458129277679795e-06</v>
       </c>
       <c r="G19">
-        <v>-0.00010312133019312096</v>
+        <v>-0.00010310867324614219</v>
       </c>
       <c r="H19">
-        <v>-1.0531834735817182e-05</v>
+        <v>-1.0525368963917522e-05</v>
       </c>
       <c r="I19">
-        <v>5.6242278751155589e-05</v>
+        <v>5.6242007746657233e-05</v>
       </c>
       <c r="J19">
-        <v>-9.6125702010555012e-05</v>
+        <v>-9.6135058073166298e-05</v>
       </c>
       <c r="K19">
-        <v>-8.8218911630923678e-05</v>
+        <v>-8.8225367978157429e-05</v>
       </c>
       <c r="L19">
-        <v>8.9686869188922505e-06</v>
+        <v>8.9718380849070079e-06</v>
       </c>
       <c r="M19">
-        <v>0.00019816916086114449</v>
+        <v>0.00019814353422234129</v>
       </c>
       <c r="N19">
-        <v>-0.00013475877993701689</v>
+        <v>-0.00013475580198615746</v>
       </c>
       <c r="O19">
-        <v>-0.00023726867942062057</v>
+        <v>-0.00023726552909100469</v>
       </c>
       <c r="P19">
-        <v>-0.0002223099108256796</v>
+        <v>-0.00022232402094960217</v>
       </c>
       <c r="Q19">
-        <v>-0.00017545685128278954</v>
+        <v>-0.00017545425546831969</v>
       </c>
       <c r="R19">
-        <v>-7.5717247819548621e-05</v>
+        <v>-7.5732908092537594e-05</v>
       </c>
       <c r="S19">
-        <v>6.8027077843045396e-05</v>
+        <v>6.8029409632777618e-05</v>
       </c>
       <c r="T19">
-        <v>0.0019759875732005688</v>
+        <v>0.0019759831171272373</v>
       </c>
       <c r="U19">
-        <v>-5.5344487735681328e-05</v>
+        <v>-5.5344365716128582e-05</v>
       </c>
       <c r="V19">
-        <v>-0.0010599985912294859</v>
+        <v>-0.0010599928528975738</v>
       </c>
       <c r="W19">
-        <v>-0.0012653091098635645</v>
+        <v>-0.001265302460738965</v>
       </c>
       <c r="X19">
-        <v>-0.018078121227259852</v>
+        <v>-0.018078021152834675</v>
       </c>
     </row>
     <row r="20">
@@ -1752,73 +1752,73 @@
         <v>42</v>
       </c>
       <c r="B20">
-        <v>0.00063940039914026255</v>
+        <v>0.00063950679816398236</v>
       </c>
       <c r="C20">
-        <v>-1.4625722378776959e-06</v>
+        <v>-1.4625903215741053e-06</v>
       </c>
       <c r="D20">
-        <v>-3.1160991750794735e-06</v>
+        <v>-3.1159961708303546e-06</v>
       </c>
       <c r="E20">
-        <v>5.4084854896824453e-08</v>
+        <v>5.4083392637728923e-08</v>
       </c>
       <c r="F20">
-        <v>-2.4759198650939324e-07</v>
+        <v>-2.4779592328197993e-07</v>
       </c>
       <c r="G20">
-        <v>3.0832572248803091e-06</v>
+        <v>3.082919824088867e-06</v>
       </c>
       <c r="H20">
-        <v>1.5946930852112648e-06</v>
+        <v>1.5945043417644762e-06</v>
       </c>
       <c r="I20">
-        <v>1.2974849833140181e-07</v>
+        <v>1.2973634851704409e-07</v>
       </c>
       <c r="J20">
-        <v>2.9446519803338951e-06</v>
+        <v>2.9449056855750877e-06</v>
       </c>
       <c r="K20">
-        <v>3.1613170862366136e-06</v>
+        <v>3.1614972443156611e-06</v>
       </c>
       <c r="L20">
-        <v>1.4273821014347467e-06</v>
+        <v>1.4272829273948083e-06</v>
       </c>
       <c r="M20">
-        <v>-3.4100503994572004e-06</v>
+        <v>-3.4093718161446124e-06</v>
       </c>
       <c r="N20">
-        <v>4.0985624615884678e-06</v>
+        <v>4.0984826773624619e-06</v>
       </c>
       <c r="O20">
-        <v>6.5815820905024979e-06</v>
+        <v>6.581508386615578e-06</v>
       </c>
       <c r="P20">
-        <v>5.8361982959960341e-06</v>
+        <v>5.8366217142982716e-06</v>
       </c>
       <c r="Q20">
-        <v>4.9997948275196962e-06</v>
+        <v>4.9997249209014281e-06</v>
       </c>
       <c r="R20">
-        <v>2.0100475070293733e-06</v>
+        <v>2.0104623675935016e-06</v>
       </c>
       <c r="S20">
-        <v>-2.1484180467304457e-06</v>
+        <v>-2.1484853374178993e-06</v>
       </c>
       <c r="T20">
-        <v>-5.5344487735681328e-05</v>
+        <v>-5.5344365716128582e-05</v>
       </c>
       <c r="U20">
-        <v>1.561886188496732e-06</v>
+        <v>1.5618828241730698e-06</v>
       </c>
       <c r="V20">
-        <v>3.0533617086172119e-05</v>
+        <v>3.0533459606117989e-05</v>
       </c>
       <c r="W20">
-        <v>3.5618141225642939e-05</v>
+        <v>3.5617959601002102e-05</v>
       </c>
       <c r="X20">
-        <v>0.00049386666752100281</v>
+        <v>0.00049386398030406382</v>
       </c>
     </row>
     <row r="21">
@@ -1826,73 +1826,73 @@
         <v>43</v>
       </c>
       <c r="B21">
-        <v>0.010069726166245151</v>
+        <v>0.010077392559145075</v>
       </c>
       <c r="C21">
-        <v>-3.3936668521710248e-05</v>
+        <v>-3.3938422846402396e-05</v>
       </c>
       <c r="D21">
-        <v>6.8777034903890009e-05</v>
+        <v>6.8795521530521861e-05</v>
       </c>
       <c r="E21">
-        <v>-1.1470442365969847e-06</v>
+        <v>-1.1473320086405721e-06</v>
       </c>
       <c r="F21">
-        <v>-7.7177607945345104e-05</v>
+        <v>-7.7180305280802309e-05</v>
       </c>
       <c r="G21">
-        <v>0.00030752307629658177</v>
+        <v>0.00030755277614396008</v>
       </c>
       <c r="H21">
-        <v>0.00030430181189942951</v>
+        <v>0.000304289422942596</v>
       </c>
       <c r="I21">
-        <v>-1.5122510281339978e-05</v>
+        <v>-1.5156171756740017e-05</v>
       </c>
       <c r="J21">
-        <v>0.00016281705851138622</v>
+        <v>0.00016283026149205814</v>
       </c>
       <c r="K21">
-        <v>0.00066412649706449234</v>
+        <v>0.00066415493360393106</v>
       </c>
       <c r="L21">
-        <v>0.00029651833547903383</v>
+        <v>0.0002965231179308421</v>
       </c>
       <c r="M21">
-        <v>0.000274679092421036</v>
+        <v>0.00027469680377451098</v>
       </c>
       <c r="N21">
-        <v>8.9410873700590445e-06</v>
+        <v>8.9397652560736958e-06</v>
       </c>
       <c r="O21">
-        <v>6.1142790614286853e-06</v>
+        <v>6.1177803449144821e-06</v>
       </c>
       <c r="P21">
-        <v>-5.9022521819152712e-05</v>
+        <v>-5.9006254171960291e-05</v>
       </c>
       <c r="Q21">
-        <v>-0.0001536030148505355</v>
+        <v>-0.00015360392109117554</v>
       </c>
       <c r="R21">
-        <v>-0.00014850496720077177</v>
+        <v>-0.00014849576739575806</v>
       </c>
       <c r="S21">
-        <v>6.7819932254616815e-05</v>
+        <v>6.7861140385467797e-05</v>
       </c>
       <c r="T21">
-        <v>-0.0010599985912294859</v>
+        <v>-0.0010599928528975738</v>
       </c>
       <c r="U21">
-        <v>3.0533617086172119e-05</v>
+        <v>3.0533459606117989e-05</v>
       </c>
       <c r="V21">
-        <v>0.0051156587756846159</v>
+        <v>0.0051157560479878506</v>
       </c>
       <c r="W21">
-        <v>0.0010107009962170047</v>
+        <v>0.0010106949839120921</v>
       </c>
       <c r="X21">
-        <v>0.0068421805215586745</v>
+        <v>0.0068418271327511035</v>
       </c>
     </row>
     <row r="22">
@@ -1900,73 +1900,73 @@
         <v>44</v>
       </c>
       <c r="B22">
-        <v>0.10849500637235385</v>
+        <v>0.10849660496121936</v>
       </c>
       <c r="C22">
-        <v>-5.7896347274442997e-05</v>
+        <v>-5.7895343697502466e-05</v>
       </c>
       <c r="D22">
-        <v>5.0760675005927843e-05</v>
+        <v>5.0764331294595941e-05</v>
       </c>
       <c r="E22">
-        <v>-7.9918909258955837e-07</v>
+        <v>-7.9924390415077263e-07</v>
       </c>
       <c r="F22">
-        <v>-1.5566382281419363e-05</v>
+        <v>-1.5570360313795309e-05</v>
       </c>
       <c r="G22">
-        <v>0.00021341875920975197</v>
+        <v>0.00021340940698398082</v>
       </c>
       <c r="H22">
-        <v>0.00032414463242732595</v>
+        <v>0.00032413422547955192</v>
       </c>
       <c r="I22">
-        <v>0.00028354475444172843</v>
+        <v>0.00028353766856027327</v>
       </c>
       <c r="J22">
-        <v>0.00019480973464896791</v>
+        <v>0.00019481291438440613</v>
       </c>
       <c r="K22">
-        <v>0.00045098363341509475</v>
+        <v>0.0004509843284580047</v>
       </c>
       <c r="L22">
-        <v>0.00042203502081150342</v>
+        <v>0.00042202505415091544</v>
       </c>
       <c r="M22">
-        <v>0.0004251835490145029</v>
+        <v>0.00042520346007512153</v>
       </c>
       <c r="N22">
-        <v>0.00019487591678812052</v>
+        <v>0.00019487508370256979</v>
       </c>
       <c r="O22">
-        <v>0.00026289092223410939</v>
+        <v>0.00026288953207990876</v>
       </c>
       <c r="P22">
-        <v>0.00010752368533522964</v>
+        <v>0.00010753854138199751</v>
       </c>
       <c r="Q22">
-        <v>9.4302004474083856e-05</v>
+        <v>9.4301582570887558e-05</v>
       </c>
       <c r="R22">
-        <v>-1.5778325103062239e-05</v>
+        <v>-1.5764205119582486e-05</v>
       </c>
       <c r="S22">
-        <v>-8.0915305141382194e-05</v>
+        <v>-8.0915287765655035e-05</v>
       </c>
       <c r="T22">
-        <v>-0.0012653091098635645</v>
+        <v>-0.001265302460738965</v>
       </c>
       <c r="U22">
-        <v>3.5618141225642939e-05</v>
+        <v>3.5617959601002102e-05</v>
       </c>
       <c r="V22">
-        <v>0.0010107009962170047</v>
+        <v>0.0010106949839120921</v>
       </c>
       <c r="W22">
-        <v>0.00521623053065074</v>
+        <v>0.0052162292764377739</v>
       </c>
       <c r="X22">
-        <v>0.0088187086907706019</v>
+        <v>0.0088185988442415</v>
       </c>
     </row>
     <row r="23">
@@ -1974,73 +1974,73 @@
         <v>45</v>
       </c>
       <c r="B23">
-        <v>-2.2645283444547202</v>
+        <v>-2.2645044970591171</v>
       </c>
       <c r="C23">
-        <v>-0.00071988674260084463</v>
+        <v>-0.00071986017024027946</v>
       </c>
       <c r="D23">
-        <v>-0.01299406356235619</v>
+        <v>-0.012994024759596448</v>
       </c>
       <c r="E23">
-        <v>0.00021073224258589824</v>
+        <v>0.00021073170872462849</v>
       </c>
       <c r="F23">
-        <v>-0.0040299053605443863</v>
+        <v>-0.0040299743959961339</v>
       </c>
       <c r="G23">
-        <v>-0.0030191850748167055</v>
+        <v>-0.003019354599321511</v>
       </c>
       <c r="H23">
-        <v>-0.020722066198303066</v>
+        <v>-0.020722099993364121</v>
       </c>
       <c r="I23">
-        <v>-0.014595033450607559</v>
+        <v>-0.014595027911356577</v>
       </c>
       <c r="J23">
-        <v>0.00017159367223051544</v>
+        <v>0.00017165430327413782</v>
       </c>
       <c r="K23">
-        <v>-0.011377583552645898</v>
+        <v>-0.011377525304068124</v>
       </c>
       <c r="L23">
-        <v>-0.013588985962256349</v>
+        <v>-0.013589054405601798</v>
       </c>
       <c r="M23">
-        <v>-0.016825164866262482</v>
+        <v>-0.016824856430950185</v>
       </c>
       <c r="N23">
-        <v>-0.0063563241374388312</v>
+        <v>-0.0063563702091149338</v>
       </c>
       <c r="O23">
-        <v>-0.0035611039623777846</v>
+        <v>-0.0035611540773963085</v>
       </c>
       <c r="P23">
-        <v>-0.0041223395296215576</v>
+        <v>-0.004122174778308986</v>
       </c>
       <c r="Q23">
-        <v>-0.0051179308176552522</v>
+        <v>-0.0051179788735218612</v>
       </c>
       <c r="R23">
-        <v>-0.0073301867145243657</v>
+        <v>-0.0073300090817103175</v>
       </c>
       <c r="S23">
-        <v>-0.0083973349829026753</v>
+        <v>-0.0083974354665247476</v>
       </c>
       <c r="T23">
-        <v>-0.018078121227259852</v>
+        <v>-0.018078021152834675</v>
       </c>
       <c r="U23">
-        <v>0.00049386666752100281</v>
+        <v>0.00049386398030406382</v>
       </c>
       <c r="V23">
-        <v>0.0068421805215586745</v>
+        <v>0.0068418271327511035</v>
       </c>
       <c r="W23">
-        <v>0.0088187086907706019</v>
+        <v>0.0088185988442415</v>
       </c>
       <c r="X23">
-        <v>0.37054147717811947</v>
+        <v>0.37054000333481318</v>
       </c>
     </row>
   </sheetData>

--- a/input/ES/reg_leave_parental_home.xlsx
+++ b/input/ES/reg_leave_parental_home.xlsx
@@ -305,7 +305,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>0.099704223872782327</v>
+        <v>0.099737861836779462</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
@@ -313,7 +313,7 @@
         <v>20</v>
       </c>
       <c r="F5">
-        <v>749.98690927615462</v>
+        <v>749.68635080984154</v>
       </c>
     </row>
     <row r="6">
@@ -329,7 +329,7 @@
         <v>21</v>
       </c>
       <c r="F6">
-        <v>-7951357.9052014332</v>
+        <v>-7951058.3205562029</v>
       </c>
     </row>
   </sheetData>
@@ -420,73 +420,73 @@
         <v>24</v>
       </c>
       <c r="B2">
-        <v>0.0006691540271923555</v>
+        <v>0.00065615708888948376</v>
       </c>
       <c r="C2">
-        <v>0.0012234312212376765</v>
+        <v>0.0012234664271415085</v>
       </c>
       <c r="D2">
-        <v>1.4669868148521971e-05</v>
+        <v>1.5203538112367274e-05</v>
       </c>
       <c r="E2">
-        <v>-3.3499323967960869e-07</v>
+        <v>-3.4391449454810735e-07</v>
       </c>
       <c r="F2">
-        <v>-8.514418116565512e-05</v>
+        <v>-8.4340299910277408e-05</v>
       </c>
       <c r="G2">
-        <v>-0.00021651781725157227</v>
+        <v>-0.0002166729463104863</v>
       </c>
       <c r="H2">
-        <v>-7.2676496969029182e-05</v>
+        <v>-6.8460652281416982e-05</v>
       </c>
       <c r="I2">
-        <v>-0.00022638279337677933</v>
+        <v>-0.00021947745258060256</v>
       </c>
       <c r="J2">
-        <v>-0.00012150450498448237</v>
+        <v>-0.00011640015233480551</v>
       </c>
       <c r="K2">
-        <v>-0.00023581320292812827</v>
+        <v>-0.00023149044581289994</v>
       </c>
       <c r="L2">
-        <v>-0.00042888195471345151</v>
+        <v>-0.00042268771915312013</v>
       </c>
       <c r="M2">
-        <v>-0.00028647655231701669</v>
+        <v>-0.00028016283720664389</v>
       </c>
       <c r="N2">
-        <v>-0.00021378693991043791</v>
+        <v>-0.00021386968304956189</v>
       </c>
       <c r="O2">
-        <v>-0.00044611502696220452</v>
+        <v>-0.00044613301170353748</v>
       </c>
       <c r="P2">
-        <v>-0.00025006872353346707</v>
+        <v>-0.00025025452001981242</v>
       </c>
       <c r="Q2">
-        <v>-0.00020679544211505254</v>
+        <v>-0.00020699279246892842</v>
       </c>
       <c r="R2">
-        <v>-0.00023864447035214272</v>
+        <v>-0.00023881194870156269</v>
       </c>
       <c r="S2">
-        <v>-0.00012493861360414799</v>
+        <v>-0.00012498396672796757</v>
       </c>
       <c r="T2">
-        <v>5.7394808335676396e-05</v>
+        <v>5.7803058717034078e-05</v>
       </c>
       <c r="U2">
-        <v>-1.4625903215741053e-06</v>
+        <v>-1.4720175283160705e-06</v>
       </c>
       <c r="V2">
-        <v>-3.3938422846402396e-05</v>
+        <v>-3.50484502690888e-05</v>
       </c>
       <c r="W2">
-        <v>-5.7895343697502466e-05</v>
+        <v>-5.8364501799373632e-05</v>
       </c>
       <c r="X2">
-        <v>-0.00071986017024027946</v>
+        <v>-0.00073818742220468957</v>
       </c>
     </row>
     <row r="3">
@@ -494,73 +494,73 @@
         <v>25</v>
       </c>
       <c r="B3">
-        <v>0.014191204787707808</v>
+        <v>0.013748329544691948</v>
       </c>
       <c r="C3">
-        <v>1.4669868148521971e-05</v>
+        <v>1.5203538112367274e-05</v>
       </c>
       <c r="D3">
-        <v>0.00075316896972869602</v>
+        <v>0.00075316796053450036</v>
       </c>
       <c r="E3">
-        <v>-1.2334603868287213e-05</v>
+        <v>-1.2333640623237088e-05</v>
       </c>
       <c r="F3">
-        <v>0.00021550188916998991</v>
+        <v>0.00021691615011561216</v>
       </c>
       <c r="G3">
-        <v>0.00023912549427157188</v>
+        <v>0.00024050722480389571</v>
       </c>
       <c r="H3">
-        <v>0.00096529786161566114</v>
+        <v>0.00096406510221643113</v>
       </c>
       <c r="I3">
-        <v>0.00051617460589646147</v>
+        <v>0.00051372287963561607</v>
       </c>
       <c r="J3">
-        <v>-7.9151621293409476e-05</v>
+        <v>-7.3056591337007301e-05</v>
       </c>
       <c r="K3">
-        <v>0.00038925838593994999</v>
+        <v>0.00038599971859775318</v>
       </c>
       <c r="L3">
-        <v>0.00042663177188269688</v>
+        <v>0.00042677291415819019</v>
       </c>
       <c r="M3">
-        <v>0.00052638173201890819</v>
+        <v>0.00052688378757877186</v>
       </c>
       <c r="N3">
-        <v>5.0698000608349371e-05</v>
+        <v>4.9349839974148144e-05</v>
       </c>
       <c r="O3">
-        <v>-2.8299989615481434e-05</v>
+        <v>-2.9368812560991685e-05</v>
       </c>
       <c r="P3">
-        <v>-1.2163438482169775e-05</v>
+        <v>-1.4255856850640698e-05</v>
       </c>
       <c r="Q3">
-        <v>4.8354368115382379e-06</v>
+        <v>3.7868783142993093e-06</v>
       </c>
       <c r="R3">
-        <v>0.00010511758577482269</v>
+        <v>0.00010337125911805839</v>
       </c>
       <c r="S3">
-        <v>9.7810087688839521e-05</v>
+        <v>9.716012804355861e-05</v>
       </c>
       <c r="T3">
-        <v>0.00012822282780917613</v>
+        <v>0.00012775922840405855</v>
       </c>
       <c r="U3">
-        <v>-3.1159961708303546e-06</v>
+        <v>-3.1001301540338933e-06</v>
       </c>
       <c r="V3">
-        <v>6.8795521530521861e-05</v>
+        <v>6.9204325351495972e-05</v>
       </c>
       <c r="W3">
-        <v>5.0764331294595941e-05</v>
+        <v>5.0068867571040083e-05</v>
       </c>
       <c r="X3">
-        <v>-0.012994024759596448</v>
+        <v>-0.012991948574733105</v>
       </c>
     </row>
     <row r="4">
@@ -568,73 +568,73 @@
         <v>26</v>
       </c>
       <c r="B4">
-        <v>0.00094038855097516166</v>
+        <v>0.00094745941079177895</v>
       </c>
       <c r="C4">
-        <v>-3.3499323967960869e-07</v>
+        <v>-3.4391449454810735e-07</v>
       </c>
       <c r="D4">
-        <v>-1.2334603868287213e-05</v>
+        <v>-1.2333640623237088e-05</v>
       </c>
       <c r="E4">
-        <v>2.0469627963097525e-07</v>
+        <v>2.0466557508217695e-07</v>
       </c>
       <c r="F4">
-        <v>-3.3401488855312521e-06</v>
+        <v>-3.3629673846064748e-06</v>
       </c>
       <c r="G4">
-        <v>-3.9871190487302237e-06</v>
+        <v>-4.0084029717566625e-06</v>
       </c>
       <c r="H4">
-        <v>-1.4662527983672973e-05</v>
+        <v>-1.463508470204432e-05</v>
       </c>
       <c r="I4">
-        <v>-8.2394700052428808e-06</v>
+        <v>-8.1873039167645554e-06</v>
       </c>
       <c r="J4">
-        <v>1.2983154209060012e-06</v>
+        <v>1.2185732831565768e-06</v>
       </c>
       <c r="K4">
-        <v>-6.0299408483846407e-06</v>
+        <v>-5.9609551246947962e-06</v>
       </c>
       <c r="L4">
-        <v>-6.6961776410212538e-06</v>
+        <v>-6.6790846878041428e-06</v>
       </c>
       <c r="M4">
-        <v>-8.4140663166382883e-06</v>
+        <v>-8.4026266000626675e-06</v>
       </c>
       <c r="N4">
-        <v>-6.2970776373695125e-07</v>
+        <v>-6.0763570088501499e-07</v>
       </c>
       <c r="O4">
-        <v>7.4946164250272397e-07</v>
+        <v>7.6628521898713996e-07</v>
       </c>
       <c r="P4">
-        <v>7.0260950129561313e-07</v>
+        <v>7.3539760203989373e-07</v>
       </c>
       <c r="Q4">
-        <v>2.9281157970790074e-07</v>
+        <v>3.0948100824583426e-07</v>
       </c>
       <c r="R4">
-        <v>-1.3766830893643849e-06</v>
+        <v>-1.3491968621790954e-06</v>
       </c>
       <c r="S4">
-        <v>-1.1986034658602746e-06</v>
+        <v>-1.1883521761748899e-06</v>
       </c>
       <c r="T4">
-        <v>-2.2111271768943239e-06</v>
+        <v>-2.2042548502646789e-06</v>
       </c>
       <c r="U4">
-        <v>5.4083392637728923e-08</v>
+        <v>5.3848220523625416e-08</v>
       </c>
       <c r="V4">
-        <v>-1.1473320086405721e-06</v>
+        <v>-1.152852131354843e-06</v>
       </c>
       <c r="W4">
-        <v>-7.9924390415077263e-07</v>
+        <v>-7.8610203081065535e-07</v>
       </c>
       <c r="X4">
-        <v>0.00021073170872462849</v>
+        <v>0.00021066792938245142</v>
       </c>
     </row>
     <row r="5">
@@ -642,73 +642,73 @@
         <v>27</v>
       </c>
       <c r="B5">
-        <v>-0.00023619045116051222</v>
+        <v>-0.00012794598056202808</v>
       </c>
       <c r="C5">
-        <v>-8.514418116565512e-05</v>
+        <v>-8.4340299910277408e-05</v>
       </c>
       <c r="D5">
-        <v>0.00021550188916998991</v>
+        <v>0.00021691615011561216</v>
       </c>
       <c r="E5">
-        <v>-3.3401488855312521e-06</v>
+        <v>-3.3629673846064748e-06</v>
       </c>
       <c r="F5">
-        <v>0.0020995182973472131</v>
+        <v>0.0021000309217793006</v>
       </c>
       <c r="G5">
-        <v>0.00076956544336188285</v>
+        <v>0.00076881793894950157</v>
       </c>
       <c r="H5">
-        <v>0.00050621547653929182</v>
+        <v>0.00051469708836648855</v>
       </c>
       <c r="I5">
-        <v>-0.000275826384741892</v>
+        <v>-0.00026473337251628519</v>
       </c>
       <c r="J5">
-        <v>-0.00022416155681528275</v>
+        <v>-0.00022731049864216824</v>
       </c>
       <c r="K5">
-        <v>-0.00037298349048661017</v>
+        <v>-0.00037028038882177481</v>
       </c>
       <c r="L5">
-        <v>-0.00037688994378195525</v>
+        <v>-0.00037291323786600586</v>
       </c>
       <c r="M5">
-        <v>-0.00017134266233243572</v>
+        <v>-0.00016643694984213965</v>
       </c>
       <c r="N5">
-        <v>0.0002430728619064479</v>
+        <v>0.00024376357390745729</v>
       </c>
       <c r="O5">
-        <v>0.00027222137713292234</v>
+        <v>0.00027235240920598335</v>
       </c>
       <c r="P5">
-        <v>0.00010859396065741265</v>
+        <v>0.00010921192015073301</v>
       </c>
       <c r="Q5">
-        <v>0.00018875902385927386</v>
+        <v>0.000188862922920542</v>
       </c>
       <c r="R5">
-        <v>0.00013268488981968971</v>
+        <v>0.00013342530116190558</v>
       </c>
       <c r="S5">
-        <v>0.0003800102323157469</v>
+        <v>0.0003811568036328095</v>
       </c>
       <c r="T5">
-        <v>9.5458129277679795e-06</v>
+        <v>9.4160122820763359e-06</v>
       </c>
       <c r="U5">
-        <v>-2.4779592328197993e-07</v>
+        <v>-2.4291663388483213e-07</v>
       </c>
       <c r="V5">
-        <v>-7.7180305280802309e-05</v>
+        <v>-7.7391398123190886e-05</v>
       </c>
       <c r="W5">
-        <v>-1.5570360313795309e-05</v>
+        <v>-1.2680358140165142e-05</v>
       </c>
       <c r="X5">
-        <v>-0.0040299743959961339</v>
+        <v>-0.0040571488768217697</v>
       </c>
     </row>
     <row r="6">
@@ -716,73 +716,73 @@
         <v>28</v>
       </c>
       <c r="B6">
-        <v>-0.040505999275069669</v>
+        <v>-0.039630439984742083</v>
       </c>
       <c r="C6">
-        <v>-0.00021651781725157227</v>
+        <v>-0.0002166729463104863</v>
       </c>
       <c r="D6">
-        <v>0.00023912549427157188</v>
+        <v>0.00024050722480389571</v>
       </c>
       <c r="E6">
-        <v>-3.9871190487302237e-06</v>
+        <v>-4.0084029717566625e-06</v>
       </c>
       <c r="F6">
-        <v>0.00076956544336188285</v>
+        <v>0.00076881793894950157</v>
       </c>
       <c r="G6">
-        <v>0.0017532680112295773</v>
+        <v>0.0017513590535978081</v>
       </c>
       <c r="H6">
-        <v>9.4220996939951493e-05</v>
+        <v>0.00010925275696802776</v>
       </c>
       <c r="I6">
-        <v>-0.00056113303383792585</v>
+        <v>-0.00053754902689653287</v>
       </c>
       <c r="J6">
-        <v>9.8775791629741525e-05</v>
+        <v>0.00011012613621925733</v>
       </c>
       <c r="K6">
-        <v>-0.00015697745422757717</v>
+        <v>-0.00013563017770506071</v>
       </c>
       <c r="L6">
-        <v>-0.00017227218027823603</v>
+        <v>-0.00015125861492166809</v>
       </c>
       <c r="M6">
-        <v>-4.0562668478525527e-05</v>
+        <v>-1.7823396696482557e-05</v>
       </c>
       <c r="N6">
-        <v>4.2647532156553456e-05</v>
+        <v>4.4388668168028524e-05</v>
       </c>
       <c r="O6">
-        <v>0.00018535194989153679</v>
+        <v>0.000185419930050969</v>
       </c>
       <c r="P6">
-        <v>-5.6527564742404543e-05</v>
+        <v>-5.5341149922082762e-05</v>
       </c>
       <c r="Q6">
-        <v>-0.00019766249395969555</v>
+        <v>-0.0001972996978428219</v>
       </c>
       <c r="R6">
-        <v>-0.00019612333935467883</v>
+        <v>-0.00019480635783829765</v>
       </c>
       <c r="S6">
-        <v>-2.1455633647065242e-05</v>
+        <v>-2.0006211669119445e-05</v>
       </c>
       <c r="T6">
-        <v>-0.00010310867324614219</v>
+        <v>-0.00010230421804188327</v>
       </c>
       <c r="U6">
-        <v>3.082919824088867e-06</v>
+        <v>3.0631193734007256e-06</v>
       </c>
       <c r="V6">
-        <v>0.00030755277614396008</v>
+        <v>0.00030545203678571868</v>
       </c>
       <c r="W6">
-        <v>0.00021340940698398082</v>
+        <v>0.00021838663581857779</v>
       </c>
       <c r="X6">
-        <v>-0.003019354599321511</v>
+        <v>-0.0030727474980253543</v>
       </c>
     </row>
     <row r="7">
@@ -790,73 +790,73 @@
         <v>29</v>
       </c>
       <c r="B7">
-        <v>-0.017475201425518578</v>
+        <v>-0.021572508801760197</v>
       </c>
       <c r="C7">
-        <v>-7.2676496969029182e-05</v>
+        <v>-6.8460652281416982e-05</v>
       </c>
       <c r="D7">
-        <v>0.00096529786161566114</v>
+        <v>0.00096406510221643113</v>
       </c>
       <c r="E7">
-        <v>-1.4662527983672973e-05</v>
+        <v>-1.463508470204432e-05</v>
       </c>
       <c r="F7">
-        <v>0.00050621547653929182</v>
+        <v>0.00051469708836648855</v>
       </c>
       <c r="G7">
-        <v>9.4220996939951493e-05</v>
+        <v>0.00010925275696802776</v>
       </c>
       <c r="H7">
-        <v>0.0067546484565675202</v>
+        <v>0.0067493319985162609</v>
       </c>
       <c r="I7">
-        <v>0.0045993246543285637</v>
+        <v>0.0045733203655450722</v>
       </c>
       <c r="J7">
-        <v>-0.00025109329655357508</v>
+        <v>-0.00025139376046632266</v>
       </c>
       <c r="K7">
-        <v>0.0035826679847354918</v>
+        <v>0.00353390485713232</v>
       </c>
       <c r="L7">
-        <v>0.0044361260610234817</v>
+        <v>0.0044202382917167722</v>
       </c>
       <c r="M7">
-        <v>0.0044388297271491014</v>
+        <v>0.0044252453996633072</v>
       </c>
       <c r="N7">
-        <v>0.00052764686844024127</v>
+        <v>0.00051843497818008545</v>
       </c>
       <c r="O7">
-        <v>-0.0002005975173697324</v>
+        <v>-0.00020894664460827626</v>
       </c>
       <c r="P7">
-        <v>5.0821662436838395e-05</v>
+        <v>3.1572104394377368e-05</v>
       </c>
       <c r="Q7">
-        <v>0.00025089081220086833</v>
+        <v>0.00024265158368176436</v>
       </c>
       <c r="R7">
-        <v>0.00028059474512940328</v>
+        <v>0.00026506240472389377</v>
       </c>
       <c r="S7">
-        <v>0.00050869178156869683</v>
+        <v>0.00050258177139202729</v>
       </c>
       <c r="T7">
-        <v>-1.0525368963917522e-05</v>
+        <v>-1.8156843543723662e-05</v>
       </c>
       <c r="U7">
-        <v>1.5945043417644762e-06</v>
+        <v>1.8307065505257969e-06</v>
       </c>
       <c r="V7">
-        <v>0.000304289422942596</v>
+        <v>0.00031509731729699279</v>
       </c>
       <c r="W7">
-        <v>0.00032413422547955192</v>
+        <v>0.00032980922440952387</v>
       </c>
       <c r="X7">
-        <v>-0.020722099993364121</v>
+        <v>-0.020634522239230485</v>
       </c>
     </row>
     <row r="8">
@@ -864,73 +864,73 @@
         <v>30</v>
       </c>
       <c r="B8">
-        <v>0.063937475399824639</v>
+        <v>0.058777689761019159</v>
       </c>
       <c r="C8">
-        <v>-0.00022638279337677933</v>
+        <v>-0.00021947745258060256</v>
       </c>
       <c r="D8">
-        <v>0.00051617460589646147</v>
+        <v>0.00051372287963561607</v>
       </c>
       <c r="E8">
-        <v>-8.2394700052428808e-06</v>
+        <v>-8.1873039167645554e-06</v>
       </c>
       <c r="F8">
-        <v>-0.000275826384741892</v>
+        <v>-0.00026473337251628519</v>
       </c>
       <c r="G8">
-        <v>-0.00056113303383792585</v>
+        <v>-0.00053754902689653287</v>
       </c>
       <c r="H8">
-        <v>0.0045993246543285637</v>
+        <v>0.0045733203655450722</v>
       </c>
       <c r="I8">
-        <v>0.0064283148073547916</v>
+        <v>0.0063631034816306765</v>
       </c>
       <c r="J8">
-        <v>0.00052040450937110077</v>
+        <v>0.00051842534642958672</v>
       </c>
       <c r="K8">
-        <v>0.0046556485770633026</v>
+        <v>0.0045817900069775354</v>
       </c>
       <c r="L8">
-        <v>0.0056122161707406193</v>
+        <v>0.0055721608497817498</v>
       </c>
       <c r="M8">
-        <v>0.0055511599359951069</v>
+        <v>0.0055132432367828157</v>
       </c>
       <c r="N8">
-        <v>0.00060661506740796768</v>
+        <v>0.00059541556126592194</v>
       </c>
       <c r="O8">
-        <v>-0.00010351475397745672</v>
+        <v>-0.00011461185300723747</v>
       </c>
       <c r="P8">
-        <v>4.4105059050825873e-05</v>
+        <v>1.804595952764566e-05</v>
       </c>
       <c r="Q8">
-        <v>0.00041848833410669355</v>
+        <v>0.00040730868248040151</v>
       </c>
       <c r="R8">
-        <v>0.00049701679275710234</v>
+        <v>0.0004770316350678452</v>
       </c>
       <c r="S8">
-        <v>7.704520214242192e-05</v>
+        <v>7.0739054208118247e-05</v>
       </c>
       <c r="T8">
-        <v>5.6242007746657233e-05</v>
+        <v>4.504284310054979e-05</v>
       </c>
       <c r="U8">
-        <v>1.2973634851704409e-07</v>
+        <v>4.6274644571503605e-07</v>
       </c>
       <c r="V8">
-        <v>-1.5156171756740017e-05</v>
+        <v>1.631160553227165e-06</v>
       </c>
       <c r="W8">
-        <v>0.00028353766856027327</v>
+        <v>0.00029148172601345065</v>
       </c>
       <c r="X8">
-        <v>-0.014595027911356577</v>
+        <v>-0.014438896889661393</v>
       </c>
     </row>
     <row r="9">
@@ -938,73 +938,73 @@
         <v>31</v>
       </c>
       <c r="B9">
-        <v>0.030897434925785172</v>
+        <v>0.038984942646395265</v>
       </c>
       <c r="C9">
-        <v>-0.00012150450498448237</v>
+        <v>-0.00011640015233480551</v>
       </c>
       <c r="D9">
-        <v>-7.9151621293409476e-05</v>
+        <v>-7.3056591337007301e-05</v>
       </c>
       <c r="E9">
-        <v>1.2983154209060012e-06</v>
+        <v>1.2185732831565768e-06</v>
       </c>
       <c r="F9">
-        <v>-0.00022416155681528275</v>
+        <v>-0.00022731049864216824</v>
       </c>
       <c r="G9">
-        <v>9.8775791629741525e-05</v>
+        <v>0.00011012613621925733</v>
       </c>
       <c r="H9">
-        <v>-0.00025109329655357508</v>
+        <v>-0.00025139376046632266</v>
       </c>
       <c r="I9">
-        <v>0.00052040450937110077</v>
+        <v>0.00051842534642958672</v>
       </c>
       <c r="J9">
-        <v>0.0029625879101285685</v>
+        <v>0.0029742027016438641</v>
       </c>
       <c r="K9">
-        <v>0.0018675283156046987</v>
+        <v>0.0018766821020148828</v>
       </c>
       <c r="L9">
-        <v>0.0019295393555241876</v>
+        <v>0.0019389306980815955</v>
       </c>
       <c r="M9">
-        <v>0.001881446829043852</v>
+        <v>0.0018914979536075629</v>
       </c>
       <c r="N9">
-        <v>-6.8613544504253238e-05</v>
+        <v>-6.17184699223185e-05</v>
       </c>
       <c r="O9">
-        <v>-4.4669134216694835e-05</v>
+        <v>-4.0407215450977813e-05</v>
       </c>
       <c r="P9">
-        <v>0.00012506335400606485</v>
+        <v>0.00012650288236911678</v>
       </c>
       <c r="Q9">
-        <v>-9.0769342035093483e-05</v>
+        <v>-9.0493570959662554e-05</v>
       </c>
       <c r="R9">
-        <v>-0.00016727071742877878</v>
+        <v>-0.00016498872727425685</v>
       </c>
       <c r="S9">
-        <v>-0.00027043139137982044</v>
+        <v>-0.00025099374776856931</v>
       </c>
       <c r="T9">
-        <v>-9.6135058073166298e-05</v>
+        <v>-9.9479715451055361e-05</v>
       </c>
       <c r="U9">
-        <v>2.9449056855750877e-06</v>
+        <v>3.0409300353068798e-06</v>
       </c>
       <c r="V9">
-        <v>0.00016283026149205814</v>
+        <v>0.00015892114693953377</v>
       </c>
       <c r="W9">
-        <v>0.00019481291438440613</v>
+        <v>0.00026515660902075462</v>
       </c>
       <c r="X9">
-        <v>0.00017165430327413782</v>
+        <v>6.450949318833471e-05</v>
       </c>
     </row>
     <row r="10">
@@ -1012,73 +1012,73 @@
         <v>32</v>
       </c>
       <c r="B10">
-        <v>0.13631486342071</v>
+        <v>0.13820842215014592</v>
       </c>
       <c r="C10">
-        <v>-0.00023581320292812827</v>
+        <v>-0.00023149044581289994</v>
       </c>
       <c r="D10">
-        <v>0.00038925838593994999</v>
+        <v>0.00038599971859775318</v>
       </c>
       <c r="E10">
-        <v>-6.0299408483846407e-06</v>
+        <v>-5.9609551246947962e-06</v>
       </c>
       <c r="F10">
-        <v>-0.00037298349048661017</v>
+        <v>-0.00037028038882177481</v>
       </c>
       <c r="G10">
-        <v>-0.00015697745422757717</v>
+        <v>-0.00013563017770506071</v>
       </c>
       <c r="H10">
-        <v>0.0035826679847354918</v>
+        <v>0.00353390485713232</v>
       </c>
       <c r="I10">
-        <v>0.0046556485770633026</v>
+        <v>0.0045817900069775354</v>
       </c>
       <c r="J10">
-        <v>0.0018675283156046987</v>
+        <v>0.0018766821020148828</v>
       </c>
       <c r="K10">
-        <v>0.0064502192139104441</v>
+        <v>0.0063853172312641092</v>
       </c>
       <c r="L10">
-        <v>0.0056576022561494206</v>
+        <v>0.0056106880410723278</v>
       </c>
       <c r="M10">
-        <v>0.0055703160817910857</v>
+        <v>0.0055248187873703728</v>
       </c>
       <c r="N10">
-        <v>0.00046642632484625909</v>
+        <v>0.00045900000957885788</v>
       </c>
       <c r="O10">
-        <v>8.3611895622163167e-05</v>
+        <v>8.3018119852866154e-05</v>
       </c>
       <c r="P10">
-        <v>4.5340411373484806e-05</v>
+        <v>2.8330729518917519e-05</v>
       </c>
       <c r="Q10">
-        <v>0.00029938065381596504</v>
+        <v>0.00029132100427676014</v>
       </c>
       <c r="R10">
-        <v>0.00038717046331863519</v>
+        <v>0.00037096586134641017</v>
       </c>
       <c r="S10">
-        <v>6.0746501642556248e-05</v>
+        <v>6.1141176271808147e-05</v>
       </c>
       <c r="T10">
-        <v>-8.8225367978157429e-05</v>
+        <v>-9.721297374143921e-05</v>
       </c>
       <c r="U10">
-        <v>3.1614972443156611e-06</v>
+        <v>3.4262043180140905e-06</v>
       </c>
       <c r="V10">
-        <v>0.00066415493360393106</v>
+        <v>0.00067050950618158679</v>
       </c>
       <c r="W10">
-        <v>0.0004509843284580047</v>
+        <v>0.00049916352481359336</v>
       </c>
       <c r="X10">
-        <v>-0.011377525304068124</v>
+        <v>-0.011226174512206123</v>
       </c>
     </row>
     <row r="11">
@@ -1086,73 +1086,73 @@
         <v>33</v>
       </c>
       <c r="B11">
-        <v>0.20447422837802501</v>
+        <v>0.20486678687991769</v>
       </c>
       <c r="C11">
-        <v>-0.00042888195471345151</v>
+        <v>-0.00042268771915312013</v>
       </c>
       <c r="D11">
-        <v>0.00042663177188269688</v>
+        <v>0.00042677291415819019</v>
       </c>
       <c r="E11">
-        <v>-6.6961776410212538e-06</v>
+        <v>-6.6790846878041428e-06</v>
       </c>
       <c r="F11">
-        <v>-0.00037688994378195525</v>
+        <v>-0.00037291323786600586</v>
       </c>
       <c r="G11">
-        <v>-0.00017227218027823603</v>
+        <v>-0.00015125861492166809</v>
       </c>
       <c r="H11">
-        <v>0.0044361260610234817</v>
+        <v>0.0044202382917167722</v>
       </c>
       <c r="I11">
-        <v>0.0056122161707406193</v>
+        <v>0.0055721608497817498</v>
       </c>
       <c r="J11">
-        <v>0.0019295393555241876</v>
+        <v>0.0019389306980815955</v>
       </c>
       <c r="K11">
-        <v>0.0056576022561494206</v>
+        <v>0.0056106880410723278</v>
       </c>
       <c r="L11">
-        <v>0.0076004122085402536</v>
+        <v>0.0075859044729598164</v>
       </c>
       <c r="M11">
-        <v>0.0064810510374092162</v>
+        <v>0.0064676509802503775</v>
       </c>
       <c r="N11">
-        <v>0.00033943992150123944</v>
+        <v>0.00033106962410869856</v>
       </c>
       <c r="O11">
-        <v>-0.00033928301937210994</v>
+        <v>-0.00034575158790057896</v>
       </c>
       <c r="P11">
-        <v>-0.00020558109344744058</v>
+        <v>-0.00022547571005406778</v>
       </c>
       <c r="Q11">
-        <v>0.00011510323199812478</v>
+        <v>0.00010585948214917283</v>
       </c>
       <c r="R11">
-        <v>8.3635695953165955e-05</v>
+        <v>6.7378819516971853e-05</v>
       </c>
       <c r="S11">
-        <v>-3.2987334583646759e-05</v>
+        <v>-3.2102021651943908e-05</v>
       </c>
       <c r="T11">
-        <v>8.9718380849070079e-06</v>
+        <v>-2.384871038966889e-06</v>
       </c>
       <c r="U11">
-        <v>1.4272829273948083e-06</v>
+        <v>1.7689952115860206e-06</v>
       </c>
       <c r="V11">
-        <v>0.0002965231179308421</v>
+        <v>0.00030715186140536357</v>
       </c>
       <c r="W11">
-        <v>0.00042202505415091544</v>
+        <v>0.0004670914748534428</v>
       </c>
       <c r="X11">
-        <v>-0.013589054405601798</v>
+        <v>-0.013508004363085004</v>
       </c>
     </row>
     <row r="12">
@@ -1160,73 +1160,73 @@
         <v>34</v>
       </c>
       <c r="B12">
-        <v>0.26801440015636496</v>
+        <v>0.26848303123604717</v>
       </c>
       <c r="C12">
-        <v>-0.00028647655231701669</v>
+        <v>-0.00028016283720664389</v>
       </c>
       <c r="D12">
-        <v>0.00052638173201890819</v>
+        <v>0.00052688378757877186</v>
       </c>
       <c r="E12">
-        <v>-8.4140663166382883e-06</v>
+        <v>-8.4026266000626675e-06</v>
       </c>
       <c r="F12">
-        <v>-0.00017134266233243572</v>
+        <v>-0.00016643694984213965</v>
       </c>
       <c r="G12">
-        <v>-4.0562668478525527e-05</v>
+        <v>-1.7823396696482557e-05</v>
       </c>
       <c r="H12">
-        <v>0.0044388297271491014</v>
+        <v>0.0044252453996633072</v>
       </c>
       <c r="I12">
-        <v>0.0055511599359951069</v>
+        <v>0.0055132432367828157</v>
       </c>
       <c r="J12">
-        <v>0.001881446829043852</v>
+        <v>0.0018914979536075629</v>
       </c>
       <c r="K12">
-        <v>0.0055703160817910857</v>
+        <v>0.0055248187873703728</v>
       </c>
       <c r="L12">
-        <v>0.0064810510374092162</v>
+        <v>0.0064676509802503775</v>
       </c>
       <c r="M12">
-        <v>0.0089540341657703623</v>
+        <v>0.008943326389953838</v>
       </c>
       <c r="N12">
-        <v>0.00029809990611835528</v>
+        <v>0.00029157666523854046</v>
       </c>
       <c r="O12">
-        <v>-0.00048245539372169816</v>
+        <v>-0.00048845609564720279</v>
       </c>
       <c r="P12">
-        <v>-0.00039253972396190813</v>
+        <v>-0.00041231845602508754</v>
       </c>
       <c r="Q12">
-        <v>9.2172585887501449e-05</v>
+        <v>8.3422281289055947e-05</v>
       </c>
       <c r="R12">
-        <v>0.00037769281730120317</v>
+        <v>0.00036186422049234068</v>
       </c>
       <c r="S12">
-        <v>-9.5581922981158481e-05</v>
+        <v>-9.3629399391339033e-05</v>
       </c>
       <c r="T12">
-        <v>0.00019814353422234129</v>
+        <v>0.00018667318576610741</v>
       </c>
       <c r="U12">
-        <v>-3.4093718161446124e-06</v>
+        <v>-3.0642025589818183e-06</v>
       </c>
       <c r="V12">
-        <v>0.00027469680377451098</v>
+        <v>0.00028548395237481703</v>
       </c>
       <c r="W12">
-        <v>0.00042520346007512153</v>
+        <v>0.0004718492814762042</v>
       </c>
       <c r="X12">
-        <v>-0.016824856430950185</v>
+        <v>-0.016752004043298949</v>
       </c>
     </row>
     <row r="13">
@@ -1234,73 +1234,73 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>0.062309783137965105</v>
+        <v>0.061654735043844708</v>
       </c>
       <c r="C13">
-        <v>-0.00021378693991043791</v>
+        <v>-0.00021386968304956189</v>
       </c>
       <c r="D13">
-        <v>5.0698000608349371e-05</v>
+        <v>4.9349839974148144e-05</v>
       </c>
       <c r="E13">
-        <v>-6.2970776373695125e-07</v>
+        <v>-6.0763570088501499e-07</v>
       </c>
       <c r="F13">
-        <v>0.0002430728619064479</v>
+        <v>0.00024376357390745729</v>
       </c>
       <c r="G13">
-        <v>4.2647532156553456e-05</v>
+        <v>4.4388668168028524e-05</v>
       </c>
       <c r="H13">
-        <v>0.00052764686844024127</v>
+        <v>0.00051843497818008545</v>
       </c>
       <c r="I13">
-        <v>0.00060661506740796768</v>
+        <v>0.00059541556126592194</v>
       </c>
       <c r="J13">
-        <v>-6.8613544504253238e-05</v>
+        <v>-6.17184699223185e-05</v>
       </c>
       <c r="K13">
-        <v>0.00046642632484625909</v>
+        <v>0.00045900000957885788</v>
       </c>
       <c r="L13">
-        <v>0.00033943992150123944</v>
+        <v>0.00033106962410869856</v>
       </c>
       <c r="M13">
-        <v>0.00029809990611835528</v>
+        <v>0.00029157666523854046</v>
       </c>
       <c r="N13">
-        <v>0.0079062224042226858</v>
+        <v>0.0079058319585405285</v>
       </c>
       <c r="O13">
-        <v>0.0060832147066223795</v>
+        <v>0.0060843044567722594</v>
       </c>
       <c r="P13">
-        <v>0.0060329687347993408</v>
+        <v>0.0060334181552498395</v>
       </c>
       <c r="Q13">
-        <v>0.0060599395698174219</v>
+        <v>0.0060602968171663205</v>
       </c>
       <c r="R13">
-        <v>0.0060284651498919463</v>
+        <v>0.0060281542541868495</v>
       </c>
       <c r="S13">
-        <v>0.0060461377633265322</v>
+        <v>0.0060457753539142831</v>
       </c>
       <c r="T13">
-        <v>-0.00013475580198615746</v>
+        <v>-0.00013496897845464507</v>
       </c>
       <c r="U13">
-        <v>4.0984826773624619e-06</v>
+        <v>4.1022909763774828e-06</v>
       </c>
       <c r="V13">
-        <v>8.9397652560736958e-06</v>
+        <v>9.4192625581285445e-06</v>
       </c>
       <c r="W13">
-        <v>0.00019487508370256979</v>
+        <v>0.00019061102470795349</v>
       </c>
       <c r="X13">
-        <v>-0.0063563702091149338</v>
+        <v>-0.0063271014685792326</v>
       </c>
     </row>
     <row r="14">
@@ -1308,73 +1308,73 @@
         <v>36</v>
       </c>
       <c r="B14">
-        <v>0.095061204651987627</v>
+        <v>0.094621431355567304</v>
       </c>
       <c r="C14">
-        <v>-0.00044611502696220452</v>
+        <v>-0.00044613301170353748</v>
       </c>
       <c r="D14">
-        <v>-2.8299989615481434e-05</v>
+        <v>-2.9368812560991685e-05</v>
       </c>
       <c r="E14">
-        <v>7.4946164250272397e-07</v>
+        <v>7.6628521898713996e-07</v>
       </c>
       <c r="F14">
-        <v>0.00027222137713292234</v>
+        <v>0.00027235240920598335</v>
       </c>
       <c r="G14">
-        <v>0.00018535194989153679</v>
+        <v>0.000185419930050969</v>
       </c>
       <c r="H14">
-        <v>-0.0002005975173697324</v>
+        <v>-0.00020894664460827626</v>
       </c>
       <c r="I14">
-        <v>-0.00010351475397745672</v>
+        <v>-0.00011461185300723747</v>
       </c>
       <c r="J14">
-        <v>-4.4669134216694835e-05</v>
+        <v>-4.0407215450977813e-05</v>
       </c>
       <c r="K14">
-        <v>8.3611895622163167e-05</v>
+        <v>8.3018119852866154e-05</v>
       </c>
       <c r="L14">
-        <v>-0.00033928301937210994</v>
+        <v>-0.00034575158790057896</v>
       </c>
       <c r="M14">
-        <v>-0.00048245539372169816</v>
+        <v>-0.00048845609564720279</v>
       </c>
       <c r="N14">
-        <v>0.0060832147066223795</v>
+        <v>0.0060843044567722594</v>
       </c>
       <c r="O14">
-        <v>0.0083957325185063068</v>
+        <v>0.008396988287321161</v>
       </c>
       <c r="P14">
-        <v>0.0061093071353620528</v>
+        <v>0.0061107476023753516</v>
       </c>
       <c r="Q14">
-        <v>0.0060891258568868539</v>
+        <v>0.0060905127327124317</v>
       </c>
       <c r="R14">
-        <v>0.0060228079270150401</v>
+        <v>0.0060238808386374396</v>
       </c>
       <c r="S14">
-        <v>0.006077739739748355</v>
+        <v>0.0060786159550495099</v>
       </c>
       <c r="T14">
-        <v>-0.00023726552909100469</v>
+        <v>-0.00023685079341013147</v>
       </c>
       <c r="U14">
-        <v>6.581508386615578e-06</v>
+        <v>6.5652559651709701e-06</v>
       </c>
       <c r="V14">
-        <v>6.1177803449144821e-06</v>
+        <v>6.0568000593331801e-06</v>
       </c>
       <c r="W14">
-        <v>0.00026288953207990876</v>
+        <v>0.00025775965630117821</v>
       </c>
       <c r="X14">
-        <v>-0.0035611540773963085</v>
+        <v>-0.0035411987867878456</v>
       </c>
     </row>
     <row r="15">
@@ -1382,73 +1382,73 @@
         <v>37</v>
       </c>
       <c r="B15">
-        <v>0.043348354726689568</v>
+        <v>0.042610009248927765</v>
       </c>
       <c r="C15">
-        <v>-0.00025006872353346707</v>
+        <v>-0.00025025452001981242</v>
       </c>
       <c r="D15">
-        <v>-1.2163438482169775e-05</v>
+        <v>-1.4255856850640698e-05</v>
       </c>
       <c r="E15">
-        <v>7.0260950129561313e-07</v>
+        <v>7.3539760203989373e-07</v>
       </c>
       <c r="F15">
-        <v>0.00010859396065741265</v>
+        <v>0.00010921192015073301</v>
       </c>
       <c r="G15">
-        <v>-5.6527564742404543e-05</v>
+        <v>-5.5341149922082762e-05</v>
       </c>
       <c r="H15">
-        <v>5.0821662436838395e-05</v>
+        <v>3.1572104394377368e-05</v>
       </c>
       <c r="I15">
-        <v>4.4105059050825873e-05</v>
+        <v>1.804595952764566e-05</v>
       </c>
       <c r="J15">
-        <v>0.00012506335400606485</v>
+        <v>0.00012650288236911678</v>
       </c>
       <c r="K15">
-        <v>4.5340411373484806e-05</v>
+        <v>2.8330729518917519e-05</v>
       </c>
       <c r="L15">
-        <v>-0.00020558109344744058</v>
+        <v>-0.00022547571005406778</v>
       </c>
       <c r="M15">
-        <v>-0.00039253972396190813</v>
+        <v>-0.00041231845602508754</v>
       </c>
       <c r="N15">
-        <v>0.0060329687347993408</v>
+        <v>0.0060334181552498395</v>
       </c>
       <c r="O15">
-        <v>0.0061093071353620528</v>
+        <v>0.0061107476023753516</v>
       </c>
       <c r="P15">
-        <v>0.0080748113456463513</v>
+        <v>0.0080750371974255275</v>
       </c>
       <c r="Q15">
-        <v>0.0060748062824215717</v>
+        <v>0.006075455506035856</v>
       </c>
       <c r="R15">
-        <v>0.0060310099561455954</v>
+        <v>0.0060314478831453404</v>
       </c>
       <c r="S15">
-        <v>0.0060699682342559083</v>
+        <v>0.0060701993349506342</v>
       </c>
       <c r="T15">
-        <v>-0.00022232402094960217</v>
+        <v>-0.00022139643100710545</v>
       </c>
       <c r="U15">
-        <v>5.8366217142982716e-06</v>
+        <v>5.8045734475495374e-06</v>
       </c>
       <c r="V15">
-        <v>-5.9006254171960291e-05</v>
+        <v>-5.9704074077526932e-05</v>
       </c>
       <c r="W15">
-        <v>0.00010753854138199751</v>
+        <v>9.9285587195904485e-05</v>
       </c>
       <c r="X15">
-        <v>-0.004122174778308986</v>
+        <v>-0.0040748479948599335</v>
       </c>
     </row>
     <row r="16">
@@ -1456,73 +1456,73 @@
         <v>38</v>
       </c>
       <c r="B16">
-        <v>0.10154441154303673</v>
+        <v>0.10097767511659538</v>
       </c>
       <c r="C16">
-        <v>-0.00020679544211505254</v>
+        <v>-0.00020699279246892842</v>
       </c>
       <c r="D16">
-        <v>4.8354368115382379e-06</v>
+        <v>3.7868783142993093e-06</v>
       </c>
       <c r="E16">
-        <v>2.9281157970790074e-07</v>
+        <v>3.0948100824583426e-07</v>
       </c>
       <c r="F16">
-        <v>0.00018875902385927386</v>
+        <v>0.000188862922920542</v>
       </c>
       <c r="G16">
-        <v>-0.00019766249395969555</v>
+        <v>-0.0001972996978428219</v>
       </c>
       <c r="H16">
-        <v>0.00025089081220086833</v>
+        <v>0.00024265158368176436</v>
       </c>
       <c r="I16">
-        <v>0.00041848833410669355</v>
+        <v>0.00040730868248040151</v>
       </c>
       <c r="J16">
-        <v>-9.0769342035093483e-05</v>
+        <v>-9.0493570959662554e-05</v>
       </c>
       <c r="K16">
-        <v>0.00029938065381596504</v>
+        <v>0.00029132100427676014</v>
       </c>
       <c r="L16">
-        <v>0.00011510323199812478</v>
+        <v>0.00010585948214917283</v>
       </c>
       <c r="M16">
-        <v>9.2172585887501449e-05</v>
+        <v>8.3422281289055947e-05</v>
       </c>
       <c r="N16">
-        <v>0.0060599395698174219</v>
+        <v>0.0060602968171663205</v>
       </c>
       <c r="O16">
-        <v>0.0060891258568868539</v>
+        <v>0.0060905127327124317</v>
       </c>
       <c r="P16">
-        <v>0.0060748062824215717</v>
+        <v>0.006075455506035856</v>
       </c>
       <c r="Q16">
-        <v>0.0077661107850402807</v>
+        <v>0.0077677700735181753</v>
       </c>
       <c r="R16">
-        <v>0.0060777083624356677</v>
+        <v>0.0060786351867444417</v>
       </c>
       <c r="S16">
-        <v>0.0060983512364471398</v>
+        <v>0.0060987604151353384</v>
       </c>
       <c r="T16">
-        <v>-0.00017545425546831969</v>
+        <v>-0.00017514912209778207</v>
       </c>
       <c r="U16">
-        <v>4.9997249209014281e-06</v>
+        <v>4.9894403468294914e-06</v>
       </c>
       <c r="V16">
-        <v>-0.00015360392109117554</v>
+        <v>-0.0001533631000139226</v>
       </c>
       <c r="W16">
-        <v>9.4301582570887558e-05</v>
+        <v>8.9398887441509141e-05</v>
       </c>
       <c r="X16">
-        <v>-0.0051179788735218612</v>
+        <v>-0.0050952208945170829</v>
       </c>
     </row>
     <row r="17">
@@ -1530,73 +1530,73 @@
         <v>39</v>
       </c>
       <c r="B17">
-        <v>0.047838733048040601</v>
+        <v>0.04714599633945947</v>
       </c>
       <c r="C17">
-        <v>-0.00023864447035214272</v>
+        <v>-0.00023881194870156269</v>
       </c>
       <c r="D17">
-        <v>0.00010511758577482269</v>
+        <v>0.00010337125911805839</v>
       </c>
       <c r="E17">
-        <v>-1.3766830893643849e-06</v>
+        <v>-1.3491968621790954e-06</v>
       </c>
       <c r="F17">
-        <v>0.00013268488981968971</v>
+        <v>0.00013342530116190558</v>
       </c>
       <c r="G17">
-        <v>-0.00019612333935467883</v>
+        <v>-0.00019480635783829765</v>
       </c>
       <c r="H17">
-        <v>0.00028059474512940328</v>
+        <v>0.00026506240472389377</v>
       </c>
       <c r="I17">
-        <v>0.00049701679275710234</v>
+        <v>0.0004770316350678452</v>
       </c>
       <c r="J17">
-        <v>-0.00016727071742877878</v>
+        <v>-0.00016498872727425685</v>
       </c>
       <c r="K17">
-        <v>0.00038717046331863519</v>
+        <v>0.00037096586134641017</v>
       </c>
       <c r="L17">
-        <v>8.3635695953165955e-05</v>
+        <v>6.7378819516971853e-05</v>
       </c>
       <c r="M17">
-        <v>0.00037769281730120317</v>
+        <v>0.00036186422049234068</v>
       </c>
       <c r="N17">
-        <v>0.0060284651498919463</v>
+        <v>0.0060281542541868495</v>
       </c>
       <c r="O17">
-        <v>0.0060228079270150401</v>
+        <v>0.0060238808386374396</v>
       </c>
       <c r="P17">
-        <v>0.0060310099561455954</v>
+        <v>0.0060314478831453404</v>
       </c>
       <c r="Q17">
-        <v>0.0060777083624356677</v>
+        <v>0.0060786351867444417</v>
       </c>
       <c r="R17">
-        <v>0.0073275801313488279</v>
+        <v>0.007328218451330866</v>
       </c>
       <c r="S17">
-        <v>0.0060798340173464699</v>
+        <v>0.0060799530693378774</v>
       </c>
       <c r="T17">
-        <v>-7.5732908092537594e-05</v>
+        <v>-7.5502927867225622e-05</v>
       </c>
       <c r="U17">
-        <v>2.0104623675935016e-06</v>
+        <v>2.0021297947229826e-06</v>
       </c>
       <c r="V17">
-        <v>-0.00014849576739575806</v>
+        <v>-0.00014839700966710846</v>
       </c>
       <c r="W17">
-        <v>-1.5764205119582486e-05</v>
+        <v>-2.1986916735142323e-05</v>
       </c>
       <c r="X17">
-        <v>-0.0073300090817103175</v>
+        <v>-0.0072879102383073546</v>
       </c>
     </row>
     <row r="18">
@@ -1604,73 +1604,73 @@
         <v>40</v>
       </c>
       <c r="B18">
-        <v>0.098192927714609857</v>
+        <v>0.098066286520625351</v>
       </c>
       <c r="C18">
-        <v>-0.00012493861360414799</v>
+        <v>-0.00012498396672796757</v>
       </c>
       <c r="D18">
-        <v>9.7810087688839521e-05</v>
+        <v>9.716012804355861e-05</v>
       </c>
       <c r="E18">
-        <v>-1.1986034658602746e-06</v>
+        <v>-1.1883521761748899e-06</v>
       </c>
       <c r="F18">
-        <v>0.0003800102323157469</v>
+        <v>0.0003811568036328095</v>
       </c>
       <c r="G18">
-        <v>-2.1455633647065242e-05</v>
+        <v>-2.0006211669119445e-05</v>
       </c>
       <c r="H18">
-        <v>0.00050869178156869683</v>
+        <v>0.00050258177139202729</v>
       </c>
       <c r="I18">
-        <v>7.704520214242192e-05</v>
+        <v>7.0739054208118247e-05</v>
       </c>
       <c r="J18">
-        <v>-0.00027043139137982044</v>
+        <v>-0.00025099374776856931</v>
       </c>
       <c r="K18">
-        <v>6.0746501642556248e-05</v>
+        <v>6.1141176271808147e-05</v>
       </c>
       <c r="L18">
-        <v>-3.2987334583646759e-05</v>
+        <v>-3.2102021651943908e-05</v>
       </c>
       <c r="M18">
-        <v>-9.5581922981158481e-05</v>
+        <v>-9.3629399391339033e-05</v>
       </c>
       <c r="N18">
-        <v>0.0060461377633265322</v>
+        <v>0.0060457753539142831</v>
       </c>
       <c r="O18">
-        <v>0.006077739739748355</v>
+        <v>0.0060786159550495099</v>
       </c>
       <c r="P18">
-        <v>0.0060699682342559083</v>
+        <v>0.0060701993349506342</v>
       </c>
       <c r="Q18">
-        <v>0.0060983512364471398</v>
+        <v>0.0060987604151353384</v>
       </c>
       <c r="R18">
-        <v>0.0060798340173464699</v>
+        <v>0.0060799530693378774</v>
       </c>
       <c r="S18">
-        <v>0.0075939321670416308</v>
+        <v>0.0075954099185975158</v>
       </c>
       <c r="T18">
-        <v>6.8029409632777618e-05</v>
+        <v>6.9357611067927087e-05</v>
       </c>
       <c r="U18">
-        <v>-2.1484853374178993e-06</v>
+        <v>-2.1863018225742805e-06</v>
       </c>
       <c r="V18">
-        <v>6.7861140385467797e-05</v>
+        <v>6.5544889841410688e-05</v>
       </c>
       <c r="W18">
-        <v>-8.0915287765655035e-05</v>
+        <v>-8.2821143871160278e-05</v>
       </c>
       <c r="X18">
-        <v>-0.0083974354665247476</v>
+        <v>-0.0084006955197906616</v>
       </c>
     </row>
     <row r="19">
@@ -1678,73 +1678,73 @@
         <v>41</v>
       </c>
       <c r="B19">
-        <v>-0.048532275959644856</v>
+        <v>-0.048259693698072204</v>
       </c>
       <c r="C19">
-        <v>5.7394808335676396e-05</v>
+        <v>5.7803058717034078e-05</v>
       </c>
       <c r="D19">
-        <v>0.00012822282780917613</v>
+        <v>0.00012775922840405855</v>
       </c>
       <c r="E19">
-        <v>-2.2111271768943239e-06</v>
+        <v>-2.2042548502646789e-06</v>
       </c>
       <c r="F19">
-        <v>9.5458129277679795e-06</v>
+        <v>9.4160122820763359e-06</v>
       </c>
       <c r="G19">
-        <v>-0.00010310867324614219</v>
+        <v>-0.00010230421804188327</v>
       </c>
       <c r="H19">
-        <v>-1.0525368963917522e-05</v>
+        <v>-1.8156843543723662e-05</v>
       </c>
       <c r="I19">
-        <v>5.6242007746657233e-05</v>
+        <v>4.504284310054979e-05</v>
       </c>
       <c r="J19">
-        <v>-9.6135058073166298e-05</v>
+        <v>-9.9479715451055361e-05</v>
       </c>
       <c r="K19">
-        <v>-8.8225367978157429e-05</v>
+        <v>-9.721297374143921e-05</v>
       </c>
       <c r="L19">
-        <v>8.9718380849070079e-06</v>
+        <v>-2.384871038966889e-06</v>
       </c>
       <c r="M19">
-        <v>0.00019814353422234129</v>
+        <v>0.00018667318576610741</v>
       </c>
       <c r="N19">
-        <v>-0.00013475580198615746</v>
+        <v>-0.00013496897845464507</v>
       </c>
       <c r="O19">
-        <v>-0.00023726552909100469</v>
+        <v>-0.00023685079341013147</v>
       </c>
       <c r="P19">
-        <v>-0.00022232402094960217</v>
+        <v>-0.00022139643100710545</v>
       </c>
       <c r="Q19">
-        <v>-0.00017545425546831969</v>
+        <v>-0.00017514912209778207</v>
       </c>
       <c r="R19">
-        <v>-7.5732908092537594e-05</v>
+        <v>-7.5502927867225622e-05</v>
       </c>
       <c r="S19">
-        <v>6.8029409632777618e-05</v>
+        <v>6.9357611067927087e-05</v>
       </c>
       <c r="T19">
-        <v>0.0019759831171272373</v>
+        <v>0.0019764746314150164</v>
       </c>
       <c r="U19">
-        <v>-5.5344365716128582e-05</v>
+        <v>-5.5360501879868351e-05</v>
       </c>
       <c r="V19">
-        <v>-0.0010599928528975738</v>
+        <v>-0.0010604976756697668</v>
       </c>
       <c r="W19">
-        <v>-0.001265302460738965</v>
+        <v>-0.0012642832473178287</v>
       </c>
       <c r="X19">
-        <v>-0.018078021152834675</v>
+        <v>-0.018063152472864441</v>
       </c>
     </row>
     <row r="20">
@@ -1752,73 +1752,73 @@
         <v>42</v>
       </c>
       <c r="B20">
-        <v>0.00063950679816398236</v>
+        <v>0.0006314306062202334</v>
       </c>
       <c r="C20">
-        <v>-1.4625903215741053e-06</v>
+        <v>-1.4720175283160705e-06</v>
       </c>
       <c r="D20">
-        <v>-3.1159961708303546e-06</v>
+        <v>-3.1001301540338933e-06</v>
       </c>
       <c r="E20">
-        <v>5.4083392637728923e-08</v>
+        <v>5.3848220523625416e-08</v>
       </c>
       <c r="F20">
-        <v>-2.4779592328197993e-07</v>
+        <v>-2.4291663388483213e-07</v>
       </c>
       <c r="G20">
-        <v>3.082919824088867e-06</v>
+        <v>3.0631193734007256e-06</v>
       </c>
       <c r="H20">
-        <v>1.5945043417644762e-06</v>
+        <v>1.8307065505257969e-06</v>
       </c>
       <c r="I20">
-        <v>1.2973634851704409e-07</v>
+        <v>4.6274644571503605e-07</v>
       </c>
       <c r="J20">
-        <v>2.9449056855750877e-06</v>
+        <v>3.0409300353068798e-06</v>
       </c>
       <c r="K20">
-        <v>3.1614972443156611e-06</v>
+        <v>3.4262043180140905e-06</v>
       </c>
       <c r="L20">
-        <v>1.4272829273948083e-06</v>
+        <v>1.7689952115860206e-06</v>
       </c>
       <c r="M20">
-        <v>-3.4093718161446124e-06</v>
+        <v>-3.0642025589818183e-06</v>
       </c>
       <c r="N20">
-        <v>4.0984826773624619e-06</v>
+        <v>4.1022909763774828e-06</v>
       </c>
       <c r="O20">
-        <v>6.581508386615578e-06</v>
+        <v>6.5652559651709701e-06</v>
       </c>
       <c r="P20">
-        <v>5.8366217142982716e-06</v>
+        <v>5.8045734475495374e-06</v>
       </c>
       <c r="Q20">
-        <v>4.9997249209014281e-06</v>
+        <v>4.9894403468294914e-06</v>
       </c>
       <c r="R20">
-        <v>2.0104623675935016e-06</v>
+        <v>2.0021297947229826e-06</v>
       </c>
       <c r="S20">
-        <v>-2.1484853374178993e-06</v>
+        <v>-2.1863018225742805e-06</v>
       </c>
       <c r="T20">
-        <v>-5.5344365716128582e-05</v>
+        <v>-5.5360501879868351e-05</v>
       </c>
       <c r="U20">
-        <v>1.5618828241730698e-06</v>
+        <v>1.5624119288160211e-06</v>
       </c>
       <c r="V20">
-        <v>3.0533459606117989e-05</v>
+        <v>3.0552032139716413e-05</v>
       </c>
       <c r="W20">
-        <v>3.5617959601002102e-05</v>
+        <v>3.559137351118424e-05</v>
       </c>
       <c r="X20">
-        <v>0.00049386398030406382</v>
+        <v>0.00049339324911737295</v>
       </c>
     </row>
     <row r="21">
@@ -1826,73 +1826,73 @@
         <v>43</v>
       </c>
       <c r="B21">
-        <v>0.010077392559145075</v>
+        <v>0.010101409849222094</v>
       </c>
       <c r="C21">
-        <v>-3.3938422846402396e-05</v>
+        <v>-3.50484502690888e-05</v>
       </c>
       <c r="D21">
-        <v>6.8795521530521861e-05</v>
+        <v>6.9204325351495972e-05</v>
       </c>
       <c r="E21">
-        <v>-1.1473320086405721e-06</v>
+        <v>-1.152852131354843e-06</v>
       </c>
       <c r="F21">
-        <v>-7.7180305280802309e-05</v>
+        <v>-7.7391398123190886e-05</v>
       </c>
       <c r="G21">
-        <v>0.00030755277614396008</v>
+        <v>0.00030545203678571868</v>
       </c>
       <c r="H21">
-        <v>0.000304289422942596</v>
+        <v>0.00031509731729699279</v>
       </c>
       <c r="I21">
-        <v>-1.5156171756740017e-05</v>
+        <v>1.631160553227165e-06</v>
       </c>
       <c r="J21">
-        <v>0.00016283026149205814</v>
+        <v>0.00015892114693953377</v>
       </c>
       <c r="K21">
-        <v>0.00066415493360393106</v>
+        <v>0.00067050950618158679</v>
       </c>
       <c r="L21">
-        <v>0.0002965231179308421</v>
+        <v>0.00030715186140536357</v>
       </c>
       <c r="M21">
-        <v>0.00027469680377451098</v>
+        <v>0.00028548395237481703</v>
       </c>
       <c r="N21">
-        <v>8.9397652560736958e-06</v>
+        <v>9.4192625581285445e-06</v>
       </c>
       <c r="O21">
-        <v>6.1177803449144821e-06</v>
+        <v>6.0568000593331801e-06</v>
       </c>
       <c r="P21">
-        <v>-5.9006254171960291e-05</v>
+        <v>-5.9704074077526932e-05</v>
       </c>
       <c r="Q21">
-        <v>-0.00015360392109117554</v>
+        <v>-0.0001533631000139226</v>
       </c>
       <c r="R21">
-        <v>-0.00014849576739575806</v>
+        <v>-0.00014839700966710846</v>
       </c>
       <c r="S21">
-        <v>6.7861140385467797e-05</v>
+        <v>6.5544889841410688e-05</v>
       </c>
       <c r="T21">
-        <v>-0.0010599928528975738</v>
+        <v>-0.0010604976756697668</v>
       </c>
       <c r="U21">
-        <v>3.0533459606117989e-05</v>
+        <v>3.0552032139716413e-05</v>
       </c>
       <c r="V21">
-        <v>0.0051157560479878506</v>
+        <v>0.0051140422162925065</v>
       </c>
       <c r="W21">
-        <v>0.0010106949839120921</v>
+        <v>0.0010129159676573341</v>
       </c>
       <c r="X21">
-        <v>0.0068418271327511035</v>
+        <v>0.0068277026096832324</v>
       </c>
     </row>
     <row r="22">
@@ -1900,73 +1900,73 @@
         <v>44</v>
       </c>
       <c r="B22">
-        <v>0.10849660496121936</v>
+        <v>0.1085291131010767</v>
       </c>
       <c r="C22">
-        <v>-5.7895343697502466e-05</v>
+        <v>-5.8364501799373632e-05</v>
       </c>
       <c r="D22">
-        <v>5.0764331294595941e-05</v>
+        <v>5.0068867571040083e-05</v>
       </c>
       <c r="E22">
-        <v>-7.9924390415077263e-07</v>
+        <v>-7.8610203081065535e-07</v>
       </c>
       <c r="F22">
-        <v>-1.5570360313795309e-05</v>
+        <v>-1.2680358140165142e-05</v>
       </c>
       <c r="G22">
-        <v>0.00021340940698398082</v>
+        <v>0.00021838663581857779</v>
       </c>
       <c r="H22">
-        <v>0.00032413422547955192</v>
+        <v>0.00032980922440952387</v>
       </c>
       <c r="I22">
-        <v>0.00028353766856027327</v>
+        <v>0.00029148172601345065</v>
       </c>
       <c r="J22">
-        <v>0.00019481291438440613</v>
+        <v>0.00026515660902075462</v>
       </c>
       <c r="K22">
-        <v>0.0004509843284580047</v>
+        <v>0.00049916352481359336</v>
       </c>
       <c r="L22">
-        <v>0.00042202505415091544</v>
+        <v>0.0004670914748534428</v>
       </c>
       <c r="M22">
-        <v>0.00042520346007512153</v>
+        <v>0.0004718492814762042</v>
       </c>
       <c r="N22">
-        <v>0.00019487508370256979</v>
+        <v>0.00019061102470795349</v>
       </c>
       <c r="O22">
-        <v>0.00026288953207990876</v>
+        <v>0.00025775965630117821</v>
       </c>
       <c r="P22">
-        <v>0.00010753854138199751</v>
+        <v>9.9285587195904485e-05</v>
       </c>
       <c r="Q22">
-        <v>9.4301582570887558e-05</v>
+        <v>8.9398887441509141e-05</v>
       </c>
       <c r="R22">
-        <v>-1.5764205119582486e-05</v>
+        <v>-2.1986916735142323e-05</v>
       </c>
       <c r="S22">
-        <v>-8.0915287765655035e-05</v>
+        <v>-8.2821143871160278e-05</v>
       </c>
       <c r="T22">
-        <v>-0.001265302460738965</v>
+        <v>-0.0012642832473178287</v>
       </c>
       <c r="U22">
-        <v>3.5617959601002102e-05</v>
+        <v>3.559137351118424e-05</v>
       </c>
       <c r="V22">
-        <v>0.0010106949839120921</v>
+        <v>0.0010129159676573341</v>
       </c>
       <c r="W22">
-        <v>0.0052162292764377739</v>
+        <v>0.0052149928617674637</v>
       </c>
       <c r="X22">
-        <v>0.0088185988442415</v>
+        <v>0.008775163646806472</v>
       </c>
     </row>
     <row r="23">
@@ -1974,73 +1974,73 @@
         <v>45</v>
       </c>
       <c r="B23">
-        <v>-2.2645044970591171</v>
+        <v>-2.2598284875852581</v>
       </c>
       <c r="C23">
-        <v>-0.00071986017024027946</v>
+        <v>-0.00073818742220468957</v>
       </c>
       <c r="D23">
-        <v>-0.012994024759596448</v>
+        <v>-0.012991948574733105</v>
       </c>
       <c r="E23">
-        <v>0.00021073170872462849</v>
+        <v>0.00021066792938245142</v>
       </c>
       <c r="F23">
-        <v>-0.0040299743959961339</v>
+        <v>-0.0040571488768217697</v>
       </c>
       <c r="G23">
-        <v>-0.003019354599321511</v>
+        <v>-0.0030727474980253543</v>
       </c>
       <c r="H23">
-        <v>-0.020722099993364121</v>
+        <v>-0.020634522239230485</v>
       </c>
       <c r="I23">
-        <v>-0.014595027911356577</v>
+        <v>-0.014438896889661393</v>
       </c>
       <c r="J23">
-        <v>0.00017165430327413782</v>
+        <v>6.450949318833471e-05</v>
       </c>
       <c r="K23">
-        <v>-0.011377525304068124</v>
+        <v>-0.011226174512206123</v>
       </c>
       <c r="L23">
-        <v>-0.013589054405601798</v>
+        <v>-0.013508004363085004</v>
       </c>
       <c r="M23">
-        <v>-0.016824856430950185</v>
+        <v>-0.016752004043298949</v>
       </c>
       <c r="N23">
-        <v>-0.0063563702091149338</v>
+        <v>-0.0063271014685792326</v>
       </c>
       <c r="O23">
-        <v>-0.0035611540773963085</v>
+        <v>-0.0035411987867878456</v>
       </c>
       <c r="P23">
-        <v>-0.004122174778308986</v>
+        <v>-0.0040748479948599335</v>
       </c>
       <c r="Q23">
-        <v>-0.0051179788735218612</v>
+        <v>-0.0050952208945170829</v>
       </c>
       <c r="R23">
-        <v>-0.0073300090817103175</v>
+        <v>-0.0072879102383073546</v>
       </c>
       <c r="S23">
-        <v>-0.0083974354665247476</v>
+        <v>-0.0084006955197906616</v>
       </c>
       <c r="T23">
-        <v>-0.018078021152834675</v>
+        <v>-0.018063152472864441</v>
       </c>
       <c r="U23">
-        <v>0.00049386398030406382</v>
+        <v>0.00049339324911737295</v>
       </c>
       <c r="V23">
-        <v>0.0068418271327511035</v>
+        <v>0.0068277026096832324</v>
       </c>
       <c r="W23">
-        <v>0.0088185988442415</v>
+        <v>0.008775163646806472</v>
       </c>
       <c r="X23">
-        <v>0.37054000333481318</v>
+        <v>0.37035737307493699</v>
       </c>
     </row>
   </sheetData>

--- a/input/ES/reg_leave_parental_home.xlsx
+++ b/input/ES/reg_leave_parental_home.xlsx
@@ -41,7 +41,7 @@
     <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
   </si>
   <si>
-    <t>15 June 2016 AK</t>
+    <t>07 Oct. 2026 AK</t>
   </si>
   <si>
     <t>Description:</t>
@@ -56,7 +56,7 @@
     <t>Goodnessoffit</t>
   </si>
   <si>
-    <t xml:space="preserve">P1 - Leaving the parental home </t>
+    <t>P1 - Leave parental home</t>
   </si>
   <si>
     <t>Pseudo R-squared</t>
@@ -256,7 +256,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -295,40 +295,34 @@
       <c r="F3"/>
     </row>
     <row r="4">
-      <c r="B4"/>
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>0.099737861836779462</v>
+      </c>
       <c r="C4"/>
       <c r="D4"/>
-      <c r="F4"/>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>749.68635080984154</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
-        <v>0.099737861836779462</v>
+        <v>26027</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5">
-        <v>749.68635080984154</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6">
-        <v>26027</v>
-      </c>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6">
         <v>-7951058.3205562029</v>
       </c>
     </row>
